--- a/CFR.SW.xlsx
+++ b/CFR.SW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7665B4-7A8E-4EDC-AA64-C3498FE9AC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD11F2E-81E1-41DC-A2FB-A45662724ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="2" xr2:uid="{F1691F7E-D160-4792-AE06-DE8123BA55BD}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="2" xr2:uid="{F1691F7E-D160-4792-AE06-DE8123BA55BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
   <si>
     <t>CFR.SW</t>
   </si>
@@ -322,7 +322,13 @@
     <t>Wholesale Growth</t>
   </si>
   <si>
-    <t>FQ126</t>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>FQ226</t>
   </si>
 </sst>
 </file>
@@ -332,13 +338,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -410,28 +422,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -788,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="J2" s="2">
-        <v>149.9</v>
+        <v>138.30000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -797,7 +812,7 @@
       </c>
       <c r="J3" s="3">
         <f>+J2*J10</f>
-        <v>158.89400000000001</v>
+        <v>146.59800000000001</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -808,10 +823,10 @@
         <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>586.70000000000005</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>94</v>
+        <v>587.6</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -823,7 +838,7 @@
       </c>
       <c r="J5" s="3">
         <f>+J3*J4</f>
-        <v>93223.109800000006</v>
+        <v>86140.984800000006</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -831,11 +846,10 @@
         <v>5</v>
       </c>
       <c r="J6" s="3">
-        <f>7606+9162</f>
-        <v>16768</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>94</v>
+        <v>7278</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -843,11 +857,11 @@
         <v>6</v>
       </c>
       <c r="J7" s="3">
-        <f>1502+4487+239+2522</f>
-        <v>8750</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>94</v>
+        <f>4486+1502</f>
+        <v>5988</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -856,7 +870,7 @@
       </c>
       <c r="J8" s="3">
         <f>+J5-J6+J7</f>
-        <v>85205.109800000006</v>
+        <v>84850.984800000006</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -982,13 +996,17 @@
         <v>1171</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="E3" s="3">
+        <v>1456</v>
+      </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3">
         <v>1295</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>1550</v>
+      </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -1022,13 +1040,17 @@
         <v>1809</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="3">
+        <v>1913</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
         <v>1731</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="3">
+        <v>1870</v>
+      </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -1062,13 +1084,17 @@
         <v>1215</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="3">
+        <v>1647</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>1335</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="3">
+        <v>1740</v>
+      </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1102,13 +1128,17 @@
         <v>603</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3">
+        <v>592</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
         <v>527</v>
       </c>
       <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="I6" s="3">
+        <v>632</v>
+      </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -1147,13 +1177,17 @@
         <v>470</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="E7" s="3">
+        <v>542</v>
+      </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3">
         <v>524</v>
       </c>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="3">
+        <v>607</v>
+      </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -1192,13 +1226,17 @@
         <v>3656</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="E8" s="3">
+        <v>4382</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
         <v>3914</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="3">
+        <v>4601</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1237,13 +1275,17 @@
         <v>911</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="E9" s="3">
+        <v>419</v>
+      </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3">
         <v>824</v>
       </c>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3">
+        <v>413</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1282,13 +1324,17 @@
         <v>701</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="E10" s="3">
+        <v>1349</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
         <v>674</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3">
+        <v>1385</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1327,13 +1373,17 @@
         <v>3631</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3">
+        <v>4501</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3">
         <v>3734</v>
       </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>4785</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1372,13 +1422,17 @@
         <v>315</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="E12" s="3">
+        <v>867</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
         <v>323</v>
       </c>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="3">
+        <v>872</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1417,13 +1471,17 @@
         <v>1322</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="E13" s="3">
+        <v>782</v>
+      </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
         <v>1355</v>
       </c>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="I13" s="3">
+        <v>742</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1462,13 +1520,17 @@
         <v>5268</v>
       </c>
       <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="10">
+        <v>6150</v>
+      </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10">
         <v>5412</v>
       </c>
       <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="I14" s="10">
+        <v>6399</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1549,9 +1611,18 @@
         <f>+G3/C3-1</f>
         <v>0.10589239965841157</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="H16" s="11" t="e">
+        <f t="shared" ref="H16:J27" si="0">+H3/D3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="11">
+        <f t="shared" si="0"/>
+        <v>6.4560439560439553E-2</v>
+      </c>
+      <c r="J16" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -1590,12 +1661,21 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="11">
-        <f t="shared" ref="G17:G27" si="0">+G4/C4-1</f>
+        <f t="shared" ref="G17:G27" si="1">+G4/C4-1</f>
         <v>-4.3117744610281949E-2</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="H17" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I17" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.2477783585990618E-2</v>
+      </c>
+      <c r="J17" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -1634,12 +1714,21 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="11">
+        <f t="shared" si="1"/>
+        <v>9.8765432098765427E-2</v>
+      </c>
+      <c r="H18" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>9.8765432098765427E-2</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I18" s="11">
+        <f t="shared" si="0"/>
+        <v>5.6466302367941701E-2</v>
+      </c>
+      <c r="J18" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -1678,12 +1767,21 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="11">
+        <f t="shared" si="1"/>
+        <v>-0.12603648424543945</v>
+      </c>
+      <c r="H19" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-0.12603648424543945</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I19" s="11">
+        <f t="shared" si="0"/>
+        <v>6.7567567567567544E-2</v>
+      </c>
+      <c r="J19" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -1722,12 +1820,21 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="11">
+        <f t="shared" si="1"/>
+        <v>0.11489361702127665</v>
+      </c>
+      <c r="H20" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>0.11489361702127665</v>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="0"/>
+        <v>0.11992619926199266</v>
+      </c>
+      <c r="J20" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -1766,12 +1873,21 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="11">
+        <f t="shared" si="1"/>
+        <v>7.0568927789934399E-2</v>
+      </c>
+      <c r="H21" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>7.0568927789934399E-2</v>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I21" s="11">
+        <f t="shared" si="0"/>
+        <v>4.9977179370150671E-2</v>
+      </c>
+      <c r="J21" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -1810,12 +1926,21 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="11">
+        <f t="shared" si="1"/>
+        <v>-9.5499451152579629E-2</v>
+      </c>
+      <c r="H22" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-9.5499451152579629E-2</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I22" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.4319809069212375E-2</v>
+      </c>
+      <c r="J22" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -1854,12 +1979,21 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="11">
+        <f t="shared" si="1"/>
+        <v>-3.8516405135520682E-2</v>
+      </c>
+      <c r="H23" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>-3.8516405135520682E-2</v>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I23" s="11">
+        <f t="shared" si="0"/>
+        <v>2.6686434395848835E-2</v>
+      </c>
+      <c r="J23" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -1898,12 +2032,21 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="11">
+        <f t="shared" si="1"/>
+        <v>2.8366841090608608E-2</v>
+      </c>
+      <c r="H24" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>2.8366841090608608E-2</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I24" s="11">
+        <f t="shared" si="0"/>
+        <v>6.3097089535658846E-2</v>
+      </c>
+      <c r="J24" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -1942,12 +2085,21 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="11">
+        <f t="shared" si="1"/>
+        <v>2.5396825396825307E-2</v>
+      </c>
+      <c r="H25" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>2.5396825396825307E-2</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I25" s="11">
+        <f t="shared" si="0"/>
+        <v>5.7670126874278527E-3</v>
+      </c>
+      <c r="J25" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -1986,12 +2138,21 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="11">
+        <f t="shared" si="1"/>
+        <v>2.4962178517397904E-2</v>
+      </c>
+      <c r="H26" s="11" t="e">
         <f t="shared" si="0"/>
-        <v>2.4962178517397904E-2</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="11">
+        <f t="shared" si="0"/>
+        <v>-5.1150895140664954E-2</v>
+      </c>
+      <c r="J26" s="11" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -2030,12 +2191,21 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="12">
+        <f t="shared" si="1"/>
+        <v>2.7334851936218652E-2</v>
+      </c>
+      <c r="H27" s="12" t="e">
         <f t="shared" si="0"/>
-        <v>2.7334851936218652E-2</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="12">
+        <f t="shared" si="0"/>
+        <v>4.0487804878048816E-2</v>
+      </c>
+      <c r="J27" s="12" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -7205,7 +7375,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BD21AA-E1E0-45B8-970B-EADFB433A5B3}">
-  <dimension ref="A1:BV298"/>
+  <dimension ref="A1:BX298"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -7213,12 +7383,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:76" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:76" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>13</v>
       </c>
@@ -7243,26 +7413,32 @@
       <c r="J2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="K2" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:74" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>70</v>
       </c>
@@ -7274,33 +7450,35 @@
         <v>2253</v>
       </c>
       <c r="H3" s="3">
-        <f>+P3-G3</f>
+        <f>+R3-G3</f>
         <v>2189</v>
       </c>
       <c r="I3" s="3">
         <v>2351</v>
       </c>
       <c r="J3" s="3">
-        <f>+Q3-I3</f>
+        <f>+S3-I3</f>
         <v>2547</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>2586</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-      <c r="N3" s="3">
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3">
         <v>3351</v>
       </c>
-      <c r="O3" s="3">
+      <c r="Q3" s="3">
         <v>4371</v>
       </c>
-      <c r="P3" s="3">
+      <c r="R3" s="3">
         <v>4442</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="S3" s="3">
         <v>4898</v>
       </c>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
@@ -7313,8 +7491,10 @@
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
-    </row>
-    <row r="4" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+    </row>
+    <row r="4" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>71</v>
       </c>
@@ -7326,33 +7506,35 @@
         <v>4262</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H31" si="0">+P4-G4</f>
+        <f t="shared" ref="H4:H31" si="0">+R4-G4</f>
         <v>3958</v>
       </c>
       <c r="I4" s="3">
         <v>3449</v>
       </c>
       <c r="J4" s="3">
-        <f t="shared" ref="J4:J31" si="1">+Q4-I4</f>
+        <f t="shared" ref="J4:J31" si="1">+S4-I4</f>
         <v>3701</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>3441</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3">
         <v>7487</v>
       </c>
-      <c r="O4" s="3">
+      <c r="Q4" s="3">
         <v>7937</v>
       </c>
-      <c r="P4" s="3">
+      <c r="R4" s="3">
         <v>8220</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="S4" s="3">
         <v>7150</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -7365,8 +7547,10 @@
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
-    </row>
-    <row r="5" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="3"/>
+    </row>
+    <row r="5" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>72</v>
       </c>
@@ -7388,23 +7572,25 @@
         <f t="shared" si="1"/>
         <v>2896</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>2600</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3">
         <v>3528</v>
       </c>
-      <c r="O5" s="3">
+      <c r="Q5" s="3">
         <v>4467</v>
       </c>
-      <c r="P5" s="3">
+      <c r="R5" s="3">
         <v>4530</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="S5" s="3">
         <v>5236</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
@@ -7417,8 +7603,10 @@
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
-    </row>
-    <row r="6" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+    </row>
+    <row r="6" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>73</v>
       </c>
@@ -7440,23 +7628,25 @@
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>1027</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
         <v>1118</v>
       </c>
-      <c r="O6" s="3">
+      <c r="Q6" s="3">
         <v>1616</v>
       </c>
-      <c r="P6" s="3">
+      <c r="R6" s="3">
         <v>1751</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="S6" s="3">
         <v>2186</v>
       </c>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
@@ -7469,8 +7659,10 @@
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
-    </row>
-    <row r="7" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+    </row>
+    <row r="7" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>74</v>
       </c>
@@ -7492,23 +7684,25 @@
         <f t="shared" si="1"/>
         <v>1078</v>
       </c>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>965</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3">
         <v>1264</v>
       </c>
-      <c r="O7" s="3">
+      <c r="Q7" s="3">
         <v>1562</v>
       </c>
-      <c r="P7" s="3">
+      <c r="R7" s="3">
         <v>1673</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="S7" s="3">
         <v>1929</v>
       </c>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
@@ -7521,8 +7715,10 @@
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
-    </row>
-    <row r="8" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+    </row>
+    <row r="8" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
@@ -7544,23 +7740,25 @@
         <f t="shared" si="1"/>
         <v>6195</v>
       </c>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>5702</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3">
         <v>8293</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10036</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10704</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11476</v>
       </c>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -7573,8 +7771,10 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-    </row>
-    <row r="9" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+    </row>
+    <row r="9" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
@@ -7596,23 +7796,25 @@
         <f t="shared" si="1"/>
         <v>3488</v>
       </c>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>3456</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
-      <c r="N9" s="3">
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3">
         <v>6045</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6983</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>7001</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>6815</v>
       </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -7625,8 +7827,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
-    </row>
-    <row r="10" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+    </row>
+    <row r="10" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
@@ -7648,23 +7852,25 @@
         <f t="shared" si="1"/>
         <v>562</v>
       </c>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>490</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
-      <c r="N10" s="3">
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3">
         <v>610</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>842</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1025</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1088</v>
       </c>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -7677,8 +7883,10 @@
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
-    </row>
-    <row r="11" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+    </row>
+    <row r="11" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>41</v>
       </c>
@@ -7700,23 +7908,25 @@
         <f t="shared" si="1"/>
         <v>453</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>456</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="3">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3">
         <v>829</v>
       </c>
-      <c r="O11" s="3">
+      <c r="Q11" s="3">
         <v>963</v>
       </c>
-      <c r="P11" s="3">
+      <c r="R11" s="3">
         <v>789</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="S11" s="3">
         <v>870</v>
       </c>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -7729,8 +7939,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>42</v>
       </c>
@@ -7752,23 +7964,25 @@
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>185</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="3">
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3">
         <v>415</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>456</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>435</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>427</v>
       </c>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -7781,8 +7995,10 @@
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
-    </row>
-    <row r="13" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>43</v>
       </c>
@@ -7804,23 +8020,25 @@
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>330</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="3">
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3">
         <v>556</v>
       </c>
-      <c r="O13" s="3">
+      <c r="Q13" s="3">
         <v>673</v>
       </c>
-      <c r="P13" s="3">
+      <c r="R13" s="3">
         <v>662</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="S13" s="3">
         <v>723</v>
       </c>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -7876,8 +8094,10 @@
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
-    </row>
-    <row r="14" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW13" s="3"/>
+      <c r="BX13" s="3"/>
+    </row>
+    <row r="14" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>75</v>
       </c>
@@ -7899,23 +8119,25 @@
         <f t="shared" si="1"/>
         <v>8020</v>
       </c>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>7414</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="3">
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3">
         <v>11057</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>13497</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>14228</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>15040</v>
       </c>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -7971,8 +8193,10 @@
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
-    </row>
-    <row r="15" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW14" s="3"/>
+      <c r="BX14" s="3"/>
+    </row>
+    <row r="15" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>76</v>
       </c>
@@ -7994,23 +8218,25 @@
         <f t="shared" si="1"/>
         <v>752</v>
       </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>621</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="3">
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3">
         <v>1152</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>1294</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>1212</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>1355</v>
       </c>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
@@ -8066,8 +8292,10 @@
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
-    </row>
-    <row r="16" spans="1:74" x14ac:dyDescent="0.2">
+      <c r="BW15" s="3"/>
+      <c r="BX15" s="3"/>
+    </row>
+    <row r="16" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>77</v>
       </c>
@@ -8089,23 +8317,25 @@
         <f t="shared" si="1"/>
         <v>2550</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3">
+        <v>2584</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="3">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3">
         <v>4539</v>
       </c>
-      <c r="O16" s="3">
+      <c r="Q16" s="3">
         <v>5162</v>
       </c>
-      <c r="P16" s="3">
+      <c r="R16" s="3">
         <v>5176</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="S16" s="3">
         <v>5004</v>
       </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -8161,8 +8391,10 @@
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
-    </row>
-    <row r="17" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW16" s="3"/>
+      <c r="BX16" s="3"/>
+    </row>
+    <row r="17" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
@@ -8184,23 +8416,25 @@
         <f t="shared" si="1"/>
         <v>11322</v>
       </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
+      <c r="K17" s="10">
+        <v>10619</v>
+      </c>
+      <c r="L17" s="10"/>
       <c r="M17" s="3"/>
-      <c r="N17" s="10">
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="10">
         <v>16748</v>
       </c>
-      <c r="O17" s="10">
+      <c r="Q17" s="10">
         <v>19953</v>
       </c>
-      <c r="P17" s="10">
+      <c r="R17" s="10">
         <v>20616</v>
       </c>
-      <c r="Q17" s="10">
+      <c r="S17" s="10">
         <v>21399</v>
       </c>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
@@ -8256,8 +8490,10 @@
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
-    </row>
-    <row r="18" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW17" s="3"/>
+      <c r="BX17" s="3"/>
+    </row>
+    <row r="18" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
@@ -8279,23 +8515,25 @@
         <f t="shared" si="1"/>
         <v>3774</v>
       </c>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <v>3680</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="3">
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3">
         <v>5572</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6237</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>6580</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7080</v>
       </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
@@ -8351,8 +8589,10 @@
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
-    </row>
-    <row r="19" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW18" s="3"/>
+      <c r="BX18" s="3"/>
+    </row>
+    <row r="19" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
@@ -8385,33 +8625,36 @@
         <v>6771</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" ref="J19" si="3">+J17-J18</f>
+        <f t="shared" ref="J19:K19" si="3">+J17-J18</f>
         <v>7548</v>
       </c>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3">
+        <f t="shared" si="3"/>
+        <v>6939</v>
+      </c>
       <c r="L19" s="3"/>
-      <c r="M19" s="3">
-        <f t="shared" ref="M19:P19" si="4">+M17-M18</f>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3">
+        <f t="shared" ref="O19:R19" si="4">+O17-O18</f>
         <v>0</v>
       </c>
-      <c r="N19" s="3">
+      <c r="P19" s="3">
         <f t="shared" si="4"/>
         <v>11176</v>
       </c>
-      <c r="O19" s="3">
+      <c r="Q19" s="3">
         <f t="shared" si="4"/>
         <v>13716</v>
       </c>
-      <c r="P19" s="3">
+      <c r="R19" s="3">
         <f t="shared" si="4"/>
         <v>14036</v>
       </c>
-      <c r="Q19" s="3">
-        <f>+Q17-Q18</f>
+      <c r="S19" s="3">
+        <f>+S17-S18</f>
         <v>14319</v>
       </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
@@ -8467,8 +8710,10 @@
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
-    </row>
-    <row r="20" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW19" s="3"/>
+      <c r="BX19" s="3"/>
+    </row>
+    <row r="20" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
@@ -8490,23 +8735,25 @@
         <f t="shared" si="1"/>
         <v>2974</v>
       </c>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3">
+        <v>2725</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
-      <c r="N20" s="3">
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3">
         <v>3930</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4683</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>5244</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5631</v>
       </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
@@ -8562,8 +8809,10 @@
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
-    </row>
-    <row r="21" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW20" s="3"/>
+      <c r="BX20" s="3"/>
+    </row>
+    <row r="21" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
@@ -8585,23 +8834,25 @@
         <f t="shared" si="1"/>
         <v>1184</v>
       </c>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>875</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
-      <c r="N21" s="3">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3">
         <v>1655</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1940</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2006</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2093</v>
       </c>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
@@ -8657,8 +8908,10 @@
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
-    </row>
-    <row r="22" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW21" s="3"/>
+      <c r="BX21" s="3"/>
+    </row>
+    <row r="22" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -8680,23 +8933,25 @@
         <f t="shared" si="1"/>
         <v>1033</v>
       </c>
-      <c r="K22" s="3"/>
+      <c r="K22" s="3">
+        <v>970</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
-      <c r="N22" s="3">
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3">
         <v>1423</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>1702</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>1889</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1991</v>
       </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -8752,8 +9007,10 @@
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
-    </row>
-    <row r="23" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW22" s="3"/>
+      <c r="BX22" s="3"/>
+    </row>
+    <row r="23" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
@@ -8775,25 +9032,27 @@
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3">
+        <v>11</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
-      <c r="N23" s="3">
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3">
         <f>216+199</f>
         <v>415</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <f>103+257</f>
         <v>360</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>103</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>137</v>
       </c>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
@@ -8849,8 +9108,10 @@
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
-    </row>
-    <row r="24" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW23" s="3"/>
+      <c r="BX23" s="3"/>
+    </row>
+    <row r="24" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
@@ -8883,36 +9144,39 @@
         <v>2206</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:Q24" si="6">+J19-SUM(J20:J23)</f>
+        <f t="shared" ref="J24:S24" si="6">+J19-SUM(J20:J23)</f>
         <v>2261</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3">
+      <c r="K24" s="3">
+        <f t="shared" si="6"/>
+        <v>2358</v>
+      </c>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <f t="shared" si="6"/>
         <v>3753</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <f t="shared" si="6"/>
         <v>5031</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <f t="shared" si="6"/>
         <v>4794</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <f t="shared" si="6"/>
         <v>4467</v>
       </c>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -8968,8 +9232,10 @@
       <c r="BT24" s="3"/>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
-    </row>
-    <row r="25" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW24" s="3"/>
+      <c r="BX24" s="3"/>
+    </row>
+    <row r="25" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
@@ -8991,23 +9257,25 @@
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="K25" s="3"/>
+      <c r="K25" s="3">
+        <v>739</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="3">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3">
         <v>956</v>
       </c>
-      <c r="O25" s="3">
+      <c r="Q25" s="3">
         <v>597</v>
       </c>
-      <c r="P25" s="3">
+      <c r="R25" s="3">
         <v>787</v>
       </c>
-      <c r="Q25" s="3">
+      <c r="S25" s="3">
         <v>792</v>
       </c>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
@@ -9063,8 +9331,10 @@
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
-    </row>
-    <row r="26" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW25" s="3"/>
+      <c r="BX25" s="3"/>
+    </row>
+    <row r="26" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
@@ -9086,23 +9356,25 @@
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K26" s="3"/>
+      <c r="K26" s="3">
+        <v>581</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
-      <c r="N26" s="3">
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3">
         <v>115</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>283</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>609</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>739</v>
       </c>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -9158,8 +9430,10 @@
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
-    </row>
-    <row r="27" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW26" s="3"/>
+      <c r="BX26" s="3"/>
+    </row>
+    <row r="27" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
@@ -9181,23 +9455,25 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="K27" s="3"/>
+      <c r="K27" s="3">
+        <v>24</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="3">
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3">
         <v>31</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>41</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>39</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>75</v>
       </c>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
@@ -9253,8 +9529,10 @@
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
-    </row>
-    <row r="28" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW27" s="3"/>
+      <c r="BX27" s="3"/>
+    </row>
+    <row r="28" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>32</v>
       </c>
@@ -9287,36 +9565,39 @@
         <v>2091</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28:Q28" si="8">+J24-J25+J26+J27</f>
+        <f t="shared" ref="J28:S28" si="8">+J24-J25+J26+J27</f>
         <v>2398</v>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3">
+      <c r="K28" s="3">
+        <f t="shared" si="8"/>
+        <v>2224</v>
+      </c>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M28" s="3">
+      <c r="O28" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N28" s="3">
+      <c r="P28" s="3">
         <f t="shared" si="8"/>
         <v>2943</v>
       </c>
-      <c r="O28" s="3">
+      <c r="Q28" s="3">
         <f t="shared" si="8"/>
         <v>4758</v>
       </c>
-      <c r="P28" s="3">
+      <c r="R28" s="3">
         <f t="shared" si="8"/>
         <v>4655</v>
       </c>
-      <c r="Q28" s="3">
+      <c r="S28" s="3">
         <f t="shared" si="8"/>
         <v>4489</v>
       </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -9372,8 +9653,10 @@
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
-    </row>
-    <row r="29" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW28" s="3"/>
+      <c r="BX28" s="3"/>
+    </row>
+    <row r="29" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>33</v>
       </c>
@@ -9395,23 +9678,25 @@
         <f t="shared" si="1"/>
         <v>365</v>
       </c>
-      <c r="K29" s="3"/>
+      <c r="K29" s="3">
+        <v>428</v>
+      </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
-      <c r="N29" s="3">
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3">
         <v>494</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>847</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>837</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>727</v>
       </c>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
@@ -9467,8 +9752,10 @@
       <c r="BT29" s="3"/>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
-    </row>
-    <row r="30" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW29" s="3"/>
+      <c r="BX29" s="3"/>
+    </row>
+    <row r="30" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>34</v>
       </c>
@@ -9493,7 +9780,7 @@
         <v>2160</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30:J30" si="10">+H28-H29</f>
+        <f t="shared" ref="H30:K30" si="10">+H28-H29</f>
         <v>1658</v>
       </c>
       <c r="I30" s="3">
@@ -9504,27 +9791,30 @@
         <f t="shared" si="10"/>
         <v>2033</v>
       </c>
-      <c r="K30" s="3"/>
+      <c r="K30" s="3">
+        <f t="shared" si="10"/>
+        <v>1796</v>
+      </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
-      <c r="N30" s="3">
-        <f t="shared" ref="N30:P30" si="11">+N28-N29</f>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3">
+        <f t="shared" ref="P30:R30" si="11">+P28-P29</f>
         <v>2449</v>
       </c>
-      <c r="O30" s="3">
+      <c r="Q30" s="3">
         <f t="shared" si="11"/>
         <v>3911</v>
       </c>
-      <c r="P30" s="3">
+      <c r="R30" s="3">
         <f t="shared" si="11"/>
         <v>3818</v>
       </c>
-      <c r="Q30" s="3">
-        <f>+Q28-Q29</f>
+      <c r="S30" s="3">
+        <f>+S28-S29</f>
         <v>3762</v>
       </c>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
@@ -9580,8 +9870,10 @@
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
-    </row>
-    <row r="31" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW30" s="3"/>
+      <c r="BX30" s="3"/>
+    </row>
+    <row r="31" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>35</v>
       </c>
@@ -9603,23 +9895,25 @@
         <f t="shared" si="1"/>
         <v>-260</v>
       </c>
-      <c r="K31" s="3"/>
+      <c r="K31" s="3">
+        <v>17</v>
+      </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="3">
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3">
         <v>370</v>
       </c>
-      <c r="O31" s="3">
+      <c r="Q31" s="3">
         <v>3610</v>
       </c>
-      <c r="P31" s="3">
+      <c r="R31" s="3">
         <v>1463</v>
       </c>
-      <c r="Q31" s="3">
+      <c r="S31" s="3">
         <v>1012</v>
       </c>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
@@ -9675,8 +9969,10 @@
       <c r="BT31" s="3"/>
       <c r="BU31" s="3"/>
       <c r="BV31" s="3"/>
-    </row>
-    <row r="32" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW31" s="3"/>
+      <c r="BX31" s="3"/>
+    </row>
+    <row r="32" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
@@ -9709,33 +10005,36 @@
         <v>457</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32" si="13">+J30-J31</f>
+        <f t="shared" ref="J32:K32" si="13">+J30-J31</f>
         <v>2293</v>
       </c>
-      <c r="K32" s="3"/>
+      <c r="K32" s="3">
+        <f t="shared" si="13"/>
+        <v>1779</v>
+      </c>
       <c r="L32" s="3"/>
-      <c r="M32" s="3">
-        <f t="shared" ref="M32:P32" si="14">+M30-M31</f>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3">
+        <f t="shared" ref="O32:R32" si="14">+O30-O31</f>
         <v>0</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <f t="shared" si="14"/>
         <v>2079</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <f t="shared" si="14"/>
         <v>301</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <f t="shared" si="14"/>
         <v>2355</v>
       </c>
-      <c r="Q32" s="3">
-        <f>+Q30-Q31</f>
+      <c r="S32" s="3">
+        <f>+S30-S31</f>
         <v>2750</v>
       </c>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -9791,8 +10090,10 @@
       <c r="BT32" s="3"/>
       <c r="BU32" s="3"/>
       <c r="BV32" s="3"/>
-    </row>
-    <row r="33" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW32" s="3"/>
+      <c r="BX32" s="3"/>
+    </row>
+    <row r="33" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -9865,8 +10166,10 @@
       <c r="BT33" s="3"/>
       <c r="BU33" s="3"/>
       <c r="BV33" s="3"/>
-    </row>
-    <row r="34" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW33" s="3"/>
+      <c r="BX33" s="3"/>
+    </row>
+    <row r="34" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>37</v>
       </c>
@@ -9899,36 +10202,39 @@
         <v>0.77999658644819936</v>
       </c>
       <c r="J34" s="13">
-        <f t="shared" ref="J34" si="16">+J32/J35</f>
+        <f t="shared" ref="J34:K34" si="16">+J32/J35</f>
         <v>3.9083006647349579</v>
       </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="13" t="e">
-        <f t="shared" ref="L34:P34" si="17">+L32/L35</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M34" s="13" t="e">
-        <f t="shared" si="17"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="K34" s="13">
+        <f t="shared" si="16"/>
+        <v>3.027569775357386</v>
+      </c>
+      <c r="L34" s="13"/>
+      <c r="M34" s="3"/>
       <c r="N34" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="N34:R34" si="17">+N32/N35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="13" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P34" s="13">
+      <c r="P34" s="13" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q34" s="13" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R34" s="13">
         <f t="shared" si="17"/>
         <v>4.0857043719639137</v>
       </c>
-      <c r="Q34" s="13">
-        <f>+Q32/Q35</f>
+      <c r="S34" s="13">
+        <f>+S32/S35</f>
         <v>4.6872336799045504</v>
       </c>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -9984,8 +10290,10 @@
       <c r="BT34" s="3"/>
       <c r="BU34" s="3"/>
       <c r="BV34" s="3"/>
-    </row>
-    <row r="35" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW34" s="3"/>
+      <c r="BX34" s="3"/>
+    </row>
+    <row r="35" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>3</v>
       </c>
@@ -9997,29 +10305,31 @@
         <v>570.9</v>
       </c>
       <c r="H35" s="5">
-        <f>+P35</f>
+        <f>+R35</f>
         <v>576.4</v>
       </c>
       <c r="I35" s="5">
         <v>585.9</v>
       </c>
       <c r="J35" s="5">
-        <f>+Q35</f>
+        <f>+S35</f>
         <v>586.70000000000005</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <v>587.6</v>
+      </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-      <c r="P35" s="5">
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5">
         <v>576.4</v>
       </c>
-      <c r="Q35" s="5">
+      <c r="S35" s="5">
         <v>586.70000000000005</v>
       </c>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
       <c r="T35" s="3"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -10075,8 +10385,10 @@
       <c r="BT35" s="3"/>
       <c r="BU35" s="3"/>
       <c r="BV35" s="3"/>
-    </row>
-    <row r="36" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW35" s="3"/>
+      <c r="BX35" s="3"/>
+    </row>
+    <row r="36" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -10149,8 +10461,10 @@
       <c r="BT36" s="3"/>
       <c r="BU36" s="3"/>
       <c r="BV36" s="3"/>
-    </row>
-    <row r="37" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW36" s="3"/>
+      <c r="BX36" s="3"/>
+    </row>
+    <row r="37" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>44</v>
       </c>
@@ -10158,7 +10472,7 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="11" t="e">
-        <f t="shared" ref="F37:J42" si="18">+F8/D8-1</f>
+        <f t="shared" ref="F37:K42" si="18">+F8/D8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="11" t="e">
@@ -10177,21 +10491,24 @@
         <f t="shared" si="18"/>
         <v>0.12595419847328237</v>
       </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
+      <c r="K37" s="11">
+        <f t="shared" si="18"/>
+        <v>7.9719750047339444E-2</v>
+      </c>
+      <c r="L37" s="11"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
-      <c r="P37" s="11">
-        <f t="shared" ref="P37" si="19">+P8/O8-1</f>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="11">
+        <f t="shared" ref="R37" si="19">+R8/Q8-1</f>
         <v>6.65603826225587E-2</v>
       </c>
-      <c r="Q37" s="11">
-        <f>+Q8/P8-1</f>
+      <c r="S37" s="11">
+        <f>+S8/R8-1</f>
         <v>7.2122571001494773E-2</v>
       </c>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -10247,8 +10564,10 @@
       <c r="BT37" s="3"/>
       <c r="BU37" s="3"/>
       <c r="BV37" s="3"/>
-    </row>
-    <row r="38" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW37" s="3"/>
+      <c r="BX37" s="3"/>
+    </row>
+    <row r="38" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>45</v>
       </c>
@@ -10275,21 +10594,24 @@
         <f t="shared" si="18"/>
         <v>2.4977960622979634E-2</v>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
+      <c r="K38" s="11">
+        <f t="shared" si="18"/>
+        <v>3.8773669972948621E-2</v>
+      </c>
+      <c r="L38" s="11"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="P38" s="11">
-        <f t="shared" ref="P38:Q42" si="20">+P9/O9-1</f>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="11">
+        <f t="shared" ref="R38:S42" si="20">+R9/Q9-1</f>
         <v>2.5776886724904191E-3</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="S38" s="11">
         <f t="shared" si="20"/>
         <v>-2.6567633195257789E-2</v>
       </c>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -10345,8 +10667,10 @@
       <c r="BT38" s="3"/>
       <c r="BU38" s="3"/>
       <c r="BV38" s="3"/>
-    </row>
-    <row r="39" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW38" s="3"/>
+      <c r="BX38" s="3"/>
+    </row>
+    <row r="39" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>46</v>
       </c>
@@ -10373,21 +10697,24 @@
         <f t="shared" si="18"/>
         <v>9.3385214007781991E-2</v>
       </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
+      <c r="K39" s="11">
+        <f t="shared" si="18"/>
+        <v>-6.84410646387833E-2</v>
+      </c>
+      <c r="L39" s="11"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-      <c r="P39" s="11">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="11">
         <f t="shared" si="20"/>
         <v>0.21733966745843225</v>
       </c>
-      <c r="Q39" s="11">
+      <c r="S39" s="11">
         <f t="shared" si="20"/>
         <v>6.1463414634146396E-2</v>
       </c>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
@@ -10443,8 +10770,10 @@
       <c r="BT39" s="3"/>
       <c r="BU39" s="3"/>
       <c r="BV39" s="3"/>
-    </row>
-    <row r="40" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW39" s="3"/>
+      <c r="BX39" s="3"/>
+    </row>
+    <row r="40" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>47</v>
       </c>
@@ -10471,21 +10800,24 @@
         <f t="shared" si="18"/>
         <v>0.1048780487804879</v>
       </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
+      <c r="K40" s="11">
+        <f t="shared" si="18"/>
+        <v>9.3525179856115193E-2</v>
+      </c>
+      <c r="L40" s="11"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-      <c r="P40" s="11">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="11">
         <f t="shared" si="20"/>
         <v>-0.18068535825545173</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="S40" s="11">
         <f t="shared" si="20"/>
         <v>0.10266159695817501</v>
       </c>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -10541,8 +10873,10 @@
       <c r="BT40" s="3"/>
       <c r="BU40" s="3"/>
       <c r="BV40" s="3"/>
-    </row>
-    <row r="41" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW40" s="3"/>
+      <c r="BX40" s="3"/>
+    </row>
+    <row r="41" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>48</v>
       </c>
@@ -10569,21 +10903,24 @@
         <f t="shared" si="18"/>
         <v>4.484304932735439E-3</v>
       </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="K41" s="11">
+        <f t="shared" si="18"/>
+        <v>-8.8669950738916259E-2</v>
+      </c>
+      <c r="L41" s="11"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
-      <c r="P41" s="11">
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="11">
         <f t="shared" si="20"/>
         <v>-4.6052631578947345E-2</v>
       </c>
-      <c r="Q41" s="11">
+      <c r="S41" s="11">
         <f t="shared" si="20"/>
         <v>-1.8390804597701149E-2</v>
       </c>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
@@ -10639,8 +10976,10 @@
       <c r="BT41" s="3"/>
       <c r="BU41" s="3"/>
       <c r="BV41" s="3"/>
-    </row>
-    <row r="42" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW41" s="3"/>
+      <c r="BX41" s="3"/>
+    </row>
+    <row r="42" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>49</v>
       </c>
@@ -10667,21 +11006,24 @@
         <f t="shared" si="18"/>
         <v>0.16618075801749277</v>
       </c>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="K42" s="11">
+        <f t="shared" si="18"/>
+        <v>2.1671826625387025E-2</v>
+      </c>
+      <c r="L42" s="11"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
-      <c r="P42" s="11">
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="11">
         <f t="shared" si="20"/>
         <v>-1.6344725111441361E-2</v>
       </c>
-      <c r="Q42" s="11">
+      <c r="S42" s="11">
         <f t="shared" si="20"/>
         <v>9.2145015105740136E-2</v>
       </c>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
@@ -10737,8 +11079,10 @@
       <c r="BT42" s="3"/>
       <c r="BU42" s="3"/>
       <c r="BV42" s="3"/>
-    </row>
-    <row r="43" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW42" s="3"/>
+      <c r="BX42" s="3"/>
+    </row>
+    <row r="43" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
         <v>50</v>
       </c>
@@ -10758,31 +11102,34 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I43" s="12">
-        <f t="shared" ref="I43:J43" si="23">+I17/G17-1</f>
+        <f t="shared" ref="I43:K43" si="23">+I17/G17-1</f>
         <v>-1.4088641033166982E-2</v>
       </c>
       <c r="J43" s="12">
         <f t="shared" si="23"/>
         <v>8.9177489177489244E-2</v>
       </c>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
+      <c r="K43" s="12">
+        <f t="shared" si="23"/>
+        <v>5.3785848962984995E-2</v>
+      </c>
+      <c r="L43" s="12"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="12">
-        <f t="shared" ref="O43:P43" si="24">+O17/N17-1</f>
+      <c r="O43" s="3"/>
+      <c r="P43" s="3"/>
+      <c r="Q43" s="12">
+        <f t="shared" ref="Q43:R43" si="24">+Q17/P17-1</f>
         <v>0.19136613326964413</v>
       </c>
-      <c r="P43" s="12">
+      <c r="R43" s="12">
         <f t="shared" si="24"/>
         <v>3.3228086002105028E-2</v>
       </c>
-      <c r="Q43" s="12">
-        <f>+Q17/P17-1</f>
+      <c r="S43" s="12">
+        <f>+S17/R17-1</f>
         <v>3.7980209545983801E-2</v>
       </c>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
       <c r="T43" s="3"/>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
@@ -10838,8 +11185,10 @@
       <c r="BT43" s="3"/>
       <c r="BU43" s="3"/>
       <c r="BV43" s="3"/>
-    </row>
-    <row r="44" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW43" s="3"/>
+      <c r="BX43" s="3"/>
+    </row>
+    <row r="44" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>51</v>
       </c>
@@ -10872,36 +11221,39 @@
         <v>0.67192616850253051</v>
       </c>
       <c r="J44" s="11">
-        <f t="shared" ref="J44:Q44" si="26">+J19/J17</f>
+        <f t="shared" ref="J44:S44" si="26">+J19/J17</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="K44" s="3"/>
-      <c r="L44" s="11" t="e">
+      <c r="K44" s="11">
+        <f t="shared" ref="K44" si="27">+K19/K17</f>
+        <v>0.65345136076843391</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="11" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M44" s="11" t="e">
+      <c r="O44" s="11" t="e">
         <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N44" s="11">
+      <c r="P44" s="11">
         <f t="shared" si="26"/>
         <v>0.6673035586338667</v>
       </c>
-      <c r="O44" s="11">
+      <c r="Q44" s="11">
         <f t="shared" si="26"/>
         <v>0.6874154262516915</v>
       </c>
-      <c r="P44" s="11">
+      <c r="R44" s="11">
         <f t="shared" si="26"/>
         <v>0.68083042297244856</v>
       </c>
-      <c r="Q44" s="11">
+      <c r="S44" s="11">
         <f t="shared" si="26"/>
         <v>0.66914341791672505</v>
       </c>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
       <c r="T44" s="3"/>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
@@ -10957,33 +11309,35 @@
       <c r="BT44" s="3"/>
       <c r="BU44" s="3"/>
       <c r="BV44" s="3"/>
-    </row>
-    <row r="45" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW44" s="3"/>
+      <c r="BX44" s="3"/>
+    </row>
+    <row r="45" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C45" s="11" t="e">
-        <f t="shared" ref="C45:H45" si="27">+C24/C17</f>
+        <f t="shared" ref="C45:H45" si="28">+C24/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D45" s="11" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E45" s="11" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F45" s="11" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.25975931904901672</v>
       </c>
       <c r="H45" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.20577200577200577</v>
       </c>
       <c r="I45" s="11">
@@ -10991,36 +11345,39 @@
         <v>0.21891435943237075</v>
       </c>
       <c r="J45" s="11">
-        <f t="shared" ref="J45:Q45" si="28">+J24/J17</f>
+        <f t="shared" ref="J45:S45" si="29">+J24/J17</f>
         <v>0.1996996996996997</v>
       </c>
-      <c r="K45" s="3"/>
-      <c r="L45" s="11" t="e">
-        <f t="shared" si="28"/>
+      <c r="K45" s="11">
+        <f t="shared" ref="K45" si="30">+K24/K17</f>
+        <v>0.22205480742066108</v>
+      </c>
+      <c r="L45" s="11"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="11" t="e">
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M45" s="11" t="e">
-        <f t="shared" si="28"/>
+      <c r="O45" s="11" t="e">
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N45" s="11">
-        <f t="shared" si="28"/>
+      <c r="P45" s="11">
+        <f t="shared" si="29"/>
         <v>0.22408645808454741</v>
       </c>
-      <c r="O45" s="11">
-        <f t="shared" si="28"/>
+      <c r="Q45" s="11">
+        <f t="shared" si="29"/>
         <v>0.25214253495714928</v>
       </c>
-      <c r="P45" s="11">
-        <f t="shared" si="28"/>
+      <c r="R45" s="11">
+        <f t="shared" si="29"/>
         <v>0.23253783469150174</v>
       </c>
-      <c r="Q45" s="11">
-        <f t="shared" si="28"/>
+      <c r="S45" s="11">
+        <f t="shared" si="29"/>
         <v>0.20874807233982898</v>
       </c>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
       <c r="T45" s="3"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
@@ -11076,33 +11433,35 @@
       <c r="BT45" s="3"/>
       <c r="BU45" s="3"/>
       <c r="BV45" s="3"/>
-    </row>
-    <row r="46" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW45" s="3"/>
+      <c r="BX45" s="3"/>
+    </row>
+    <row r="46" spans="2:76" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C46" s="11" t="e">
-        <f t="shared" ref="C46:H46" si="29">+C29/C28</f>
+        <f t="shared" ref="C46:H46" si="31">+C29/C28</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F46" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.1783948269303918</v>
       </c>
       <c r="H46" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.18163869693978282</v>
       </c>
       <c r="I46" s="11">
@@ -11110,36 +11469,39 @@
         <v>0.17312290769966523</v>
       </c>
       <c r="J46" s="11">
-        <f t="shared" ref="J46:Q46" si="30">+J29/J28</f>
+        <f t="shared" ref="J46:S46" si="32">+J29/J28</f>
         <v>0.15221017514595497</v>
       </c>
-      <c r="K46" s="3"/>
-      <c r="L46" s="11" t="e">
-        <f t="shared" si="30"/>
+      <c r="K46" s="11">
+        <f t="shared" ref="K46" si="33">+K29/K28</f>
+        <v>0.19244604316546762</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="11" t="e">
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M46" s="11" t="e">
-        <f t="shared" si="30"/>
+      <c r="O46" s="11" t="e">
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N46" s="11">
-        <f t="shared" si="30"/>
+      <c r="P46" s="11">
+        <f t="shared" si="32"/>
         <v>0.16785592932381924</v>
       </c>
-      <c r="O46" s="11">
-        <f t="shared" si="30"/>
+      <c r="Q46" s="11">
+        <f t="shared" si="32"/>
         <v>0.17801597309794032</v>
       </c>
-      <c r="P46" s="11">
-        <f t="shared" si="30"/>
+      <c r="R46" s="11">
+        <f t="shared" si="32"/>
         <v>0.17980665950590763</v>
       </c>
-      <c r="Q46" s="11">
-        <f t="shared" si="30"/>
+      <c r="S46" s="11">
+        <f t="shared" si="32"/>
         <v>0.16195143684562263</v>
       </c>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -11195,8 +11557,10 @@
       <c r="BT46" s="3"/>
       <c r="BU46" s="3"/>
       <c r="BV46" s="3"/>
-    </row>
-    <row r="47" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW46" s="3"/>
+      <c r="BX46" s="3"/>
+    </row>
+    <row r="47" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -11269,8 +11633,10 @@
       <c r="BT47" s="3"/>
       <c r="BU47" s="3"/>
       <c r="BV47" s="3"/>
-    </row>
-    <row r="48" spans="2:74" x14ac:dyDescent="0.2">
+      <c r="BW47" s="3"/>
+      <c r="BX47" s="3"/>
+    </row>
+    <row r="48" spans="2:76" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -11343,8 +11709,10 @@
       <c r="BT48" s="3"/>
       <c r="BU48" s="3"/>
       <c r="BV48" s="3"/>
-    </row>
-    <row r="49" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW48" s="3"/>
+      <c r="BX48" s="3"/>
+    </row>
+    <row r="49" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -11417,8 +11785,10 @@
       <c r="BT49" s="3"/>
       <c r="BU49" s="3"/>
       <c r="BV49" s="3"/>
-    </row>
-    <row r="50" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW49" s="3"/>
+      <c r="BX49" s="3"/>
+    </row>
+    <row r="50" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -11491,8 +11861,10 @@
       <c r="BT50" s="3"/>
       <c r="BU50" s="3"/>
       <c r="BV50" s="3"/>
-    </row>
-    <row r="51" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW50" s="3"/>
+      <c r="BX50" s="3"/>
+    </row>
+    <row r="51" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -11565,8 +11937,10 @@
       <c r="BT51" s="3"/>
       <c r="BU51" s="3"/>
       <c r="BV51" s="3"/>
-    </row>
-    <row r="52" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW51" s="3"/>
+      <c r="BX51" s="3"/>
+    </row>
+    <row r="52" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -11639,8 +12013,10 @@
       <c r="BT52" s="3"/>
       <c r="BU52" s="3"/>
       <c r="BV52" s="3"/>
-    </row>
-    <row r="53" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW52" s="3"/>
+      <c r="BX52" s="3"/>
+    </row>
+    <row r="53" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -11713,8 +12089,10 @@
       <c r="BT53" s="3"/>
       <c r="BU53" s="3"/>
       <c r="BV53" s="3"/>
-    </row>
-    <row r="54" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW53" s="3"/>
+      <c r="BX53" s="3"/>
+    </row>
+    <row r="54" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -11787,8 +12165,10 @@
       <c r="BT54" s="3"/>
       <c r="BU54" s="3"/>
       <c r="BV54" s="3"/>
-    </row>
-    <row r="55" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW54" s="3"/>
+      <c r="BX54" s="3"/>
+    </row>
+    <row r="55" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -11861,8 +12241,10 @@
       <c r="BT55" s="3"/>
       <c r="BU55" s="3"/>
       <c r="BV55" s="3"/>
-    </row>
-    <row r="56" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW55" s="3"/>
+      <c r="BX55" s="3"/>
+    </row>
+    <row r="56" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -11935,8 +12317,10 @@
       <c r="BT56" s="3"/>
       <c r="BU56" s="3"/>
       <c r="BV56" s="3"/>
-    </row>
-    <row r="57" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW56" s="3"/>
+      <c r="BX56" s="3"/>
+    </row>
+    <row r="57" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -12009,8 +12393,10 @@
       <c r="BT57" s="3"/>
       <c r="BU57" s="3"/>
       <c r="BV57" s="3"/>
-    </row>
-    <row r="58" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW57" s="3"/>
+      <c r="BX57" s="3"/>
+    </row>
+    <row r="58" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -12083,8 +12469,10 @@
       <c r="BT58" s="3"/>
       <c r="BU58" s="3"/>
       <c r="BV58" s="3"/>
-    </row>
-    <row r="59" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW58" s="3"/>
+      <c r="BX58" s="3"/>
+    </row>
+    <row r="59" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -12157,8 +12545,10 @@
       <c r="BT59" s="3"/>
       <c r="BU59" s="3"/>
       <c r="BV59" s="3"/>
-    </row>
-    <row r="60" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW59" s="3"/>
+      <c r="BX59" s="3"/>
+    </row>
+    <row r="60" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -12231,8 +12621,10 @@
       <c r="BT60" s="3"/>
       <c r="BU60" s="3"/>
       <c r="BV60" s="3"/>
-    </row>
-    <row r="61" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW60" s="3"/>
+      <c r="BX60" s="3"/>
+    </row>
+    <row r="61" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -12305,8 +12697,10 @@
       <c r="BT61" s="3"/>
       <c r="BU61" s="3"/>
       <c r="BV61" s="3"/>
-    </row>
-    <row r="62" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW61" s="3"/>
+      <c r="BX61" s="3"/>
+    </row>
+    <row r="62" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -12379,8 +12773,10 @@
       <c r="BT62" s="3"/>
       <c r="BU62" s="3"/>
       <c r="BV62" s="3"/>
-    </row>
-    <row r="63" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW62" s="3"/>
+      <c r="BX62" s="3"/>
+    </row>
+    <row r="63" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -12453,8 +12849,10 @@
       <c r="BT63" s="3"/>
       <c r="BU63" s="3"/>
       <c r="BV63" s="3"/>
-    </row>
-    <row r="64" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW63" s="3"/>
+      <c r="BX63" s="3"/>
+    </row>
+    <row r="64" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -12527,8 +12925,10 @@
       <c r="BT64" s="3"/>
       <c r="BU64" s="3"/>
       <c r="BV64" s="3"/>
-    </row>
-    <row r="65" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW64" s="3"/>
+      <c r="BX64" s="3"/>
+    </row>
+    <row r="65" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -12601,8 +13001,10 @@
       <c r="BT65" s="3"/>
       <c r="BU65" s="3"/>
       <c r="BV65" s="3"/>
-    </row>
-    <row r="66" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW65" s="3"/>
+      <c r="BX65" s="3"/>
+    </row>
+    <row r="66" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -12675,8 +13077,10 @@
       <c r="BT66" s="3"/>
       <c r="BU66" s="3"/>
       <c r="BV66" s="3"/>
-    </row>
-    <row r="67" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW66" s="3"/>
+      <c r="BX66" s="3"/>
+    </row>
+    <row r="67" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -12749,8 +13153,10 @@
       <c r="BT67" s="3"/>
       <c r="BU67" s="3"/>
       <c r="BV67" s="3"/>
-    </row>
-    <row r="68" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW67" s="3"/>
+      <c r="BX67" s="3"/>
+    </row>
+    <row r="68" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -12823,8 +13229,10 @@
       <c r="BT68" s="3"/>
       <c r="BU68" s="3"/>
       <c r="BV68" s="3"/>
-    </row>
-    <row r="69" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW68" s="3"/>
+      <c r="BX68" s="3"/>
+    </row>
+    <row r="69" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -12897,8 +13305,10 @@
       <c r="BT69" s="3"/>
       <c r="BU69" s="3"/>
       <c r="BV69" s="3"/>
-    </row>
-    <row r="70" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW69" s="3"/>
+      <c r="BX69" s="3"/>
+    </row>
+    <row r="70" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -12971,8 +13381,10 @@
       <c r="BT70" s="3"/>
       <c r="BU70" s="3"/>
       <c r="BV70" s="3"/>
-    </row>
-    <row r="71" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW70" s="3"/>
+      <c r="BX70" s="3"/>
+    </row>
+    <row r="71" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -13045,8 +13457,10 @@
       <c r="BT71" s="3"/>
       <c r="BU71" s="3"/>
       <c r="BV71" s="3"/>
-    </row>
-    <row r="72" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW71" s="3"/>
+      <c r="BX71" s="3"/>
+    </row>
+    <row r="72" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -13119,8 +13533,10 @@
       <c r="BT72" s="3"/>
       <c r="BU72" s="3"/>
       <c r="BV72" s="3"/>
-    </row>
-    <row r="73" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW72" s="3"/>
+      <c r="BX72" s="3"/>
+    </row>
+    <row r="73" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -13193,8 +13609,10 @@
       <c r="BT73" s="3"/>
       <c r="BU73" s="3"/>
       <c r="BV73" s="3"/>
-    </row>
-    <row r="74" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW73" s="3"/>
+      <c r="BX73" s="3"/>
+    </row>
+    <row r="74" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -13267,8 +13685,10 @@
       <c r="BT74" s="3"/>
       <c r="BU74" s="3"/>
       <c r="BV74" s="3"/>
-    </row>
-    <row r="75" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW74" s="3"/>
+      <c r="BX74" s="3"/>
+    </row>
+    <row r="75" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -13341,8 +13761,10 @@
       <c r="BT75" s="3"/>
       <c r="BU75" s="3"/>
       <c r="BV75" s="3"/>
-    </row>
-    <row r="76" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW75" s="3"/>
+      <c r="BX75" s="3"/>
+    </row>
+    <row r="76" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -13415,8 +13837,10 @@
       <c r="BT76" s="3"/>
       <c r="BU76" s="3"/>
       <c r="BV76" s="3"/>
-    </row>
-    <row r="77" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW76" s="3"/>
+      <c r="BX76" s="3"/>
+    </row>
+    <row r="77" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -13489,8 +13913,10 @@
       <c r="BT77" s="3"/>
       <c r="BU77" s="3"/>
       <c r="BV77" s="3"/>
-    </row>
-    <row r="78" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW77" s="3"/>
+      <c r="BX77" s="3"/>
+    </row>
+    <row r="78" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -13563,8 +13989,10 @@
       <c r="BT78" s="3"/>
       <c r="BU78" s="3"/>
       <c r="BV78" s="3"/>
-    </row>
-    <row r="79" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW78" s="3"/>
+      <c r="BX78" s="3"/>
+    </row>
+    <row r="79" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -13637,8 +14065,10 @@
       <c r="BT79" s="3"/>
       <c r="BU79" s="3"/>
       <c r="BV79" s="3"/>
-    </row>
-    <row r="80" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW79" s="3"/>
+      <c r="BX79" s="3"/>
+    </row>
+    <row r="80" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -13711,8 +14141,10 @@
       <c r="BT80" s="3"/>
       <c r="BU80" s="3"/>
       <c r="BV80" s="3"/>
-    </row>
-    <row r="81" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW80" s="3"/>
+      <c r="BX80" s="3"/>
+    </row>
+    <row r="81" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -13785,8 +14217,10 @@
       <c r="BT81" s="3"/>
       <c r="BU81" s="3"/>
       <c r="BV81" s="3"/>
-    </row>
-    <row r="82" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW81" s="3"/>
+      <c r="BX81" s="3"/>
+    </row>
+    <row r="82" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -13859,8 +14293,10 @@
       <c r="BT82" s="3"/>
       <c r="BU82" s="3"/>
       <c r="BV82" s="3"/>
-    </row>
-    <row r="83" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW82" s="3"/>
+      <c r="BX82" s="3"/>
+    </row>
+    <row r="83" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -13933,8 +14369,10 @@
       <c r="BT83" s="3"/>
       <c r="BU83" s="3"/>
       <c r="BV83" s="3"/>
-    </row>
-    <row r="84" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW83" s="3"/>
+      <c r="BX83" s="3"/>
+    </row>
+    <row r="84" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -14007,8 +14445,10 @@
       <c r="BT84" s="3"/>
       <c r="BU84" s="3"/>
       <c r="BV84" s="3"/>
-    </row>
-    <row r="85" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW84" s="3"/>
+      <c r="BX84" s="3"/>
+    </row>
+    <row r="85" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -14081,8 +14521,10 @@
       <c r="BT85" s="3"/>
       <c r="BU85" s="3"/>
       <c r="BV85" s="3"/>
-    </row>
-    <row r="86" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW85" s="3"/>
+      <c r="BX85" s="3"/>
+    </row>
+    <row r="86" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -14155,8 +14597,10 @@
       <c r="BT86" s="3"/>
       <c r="BU86" s="3"/>
       <c r="BV86" s="3"/>
-    </row>
-    <row r="87" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW86" s="3"/>
+      <c r="BX86" s="3"/>
+    </row>
+    <row r="87" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -14229,8 +14673,10 @@
       <c r="BT87" s="3"/>
       <c r="BU87" s="3"/>
       <c r="BV87" s="3"/>
-    </row>
-    <row r="88" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW87" s="3"/>
+      <c r="BX87" s="3"/>
+    </row>
+    <row r="88" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -14303,8 +14749,10 @@
       <c r="BT88" s="3"/>
       <c r="BU88" s="3"/>
       <c r="BV88" s="3"/>
-    </row>
-    <row r="89" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW88" s="3"/>
+      <c r="BX88" s="3"/>
+    </row>
+    <row r="89" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -14377,8 +14825,10 @@
       <c r="BT89" s="3"/>
       <c r="BU89" s="3"/>
       <c r="BV89" s="3"/>
-    </row>
-    <row r="90" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW89" s="3"/>
+      <c r="BX89" s="3"/>
+    </row>
+    <row r="90" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -14451,8 +14901,10 @@
       <c r="BT90" s="3"/>
       <c r="BU90" s="3"/>
       <c r="BV90" s="3"/>
-    </row>
-    <row r="91" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW90" s="3"/>
+      <c r="BX90" s="3"/>
+    </row>
+    <row r="91" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -14525,8 +14977,10 @@
       <c r="BT91" s="3"/>
       <c r="BU91" s="3"/>
       <c r="BV91" s="3"/>
-    </row>
-    <row r="92" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW91" s="3"/>
+      <c r="BX91" s="3"/>
+    </row>
+    <row r="92" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -14599,8 +15053,10 @@
       <c r="BT92" s="3"/>
       <c r="BU92" s="3"/>
       <c r="BV92" s="3"/>
-    </row>
-    <row r="93" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW92" s="3"/>
+      <c r="BX92" s="3"/>
+    </row>
+    <row r="93" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -14673,8 +15129,10 @@
       <c r="BT93" s="3"/>
       <c r="BU93" s="3"/>
       <c r="BV93" s="3"/>
-    </row>
-    <row r="94" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW93" s="3"/>
+      <c r="BX93" s="3"/>
+    </row>
+    <row r="94" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -14747,8 +15205,10 @@
       <c r="BT94" s="3"/>
       <c r="BU94" s="3"/>
       <c r="BV94" s="3"/>
-    </row>
-    <row r="95" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW94" s="3"/>
+      <c r="BX94" s="3"/>
+    </row>
+    <row r="95" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -14821,8 +15281,10 @@
       <c r="BT95" s="3"/>
       <c r="BU95" s="3"/>
       <c r="BV95" s="3"/>
-    </row>
-    <row r="96" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW95" s="3"/>
+      <c r="BX95" s="3"/>
+    </row>
+    <row r="96" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -14895,8 +15357,10 @@
       <c r="BT96" s="3"/>
       <c r="BU96" s="3"/>
       <c r="BV96" s="3"/>
-    </row>
-    <row r="97" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW96" s="3"/>
+      <c r="BX96" s="3"/>
+    </row>
+    <row r="97" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -14969,8 +15433,10 @@
       <c r="BT97" s="3"/>
       <c r="BU97" s="3"/>
       <c r="BV97" s="3"/>
-    </row>
-    <row r="98" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW97" s="3"/>
+      <c r="BX97" s="3"/>
+    </row>
+    <row r="98" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -15043,8 +15509,10 @@
       <c r="BT98" s="3"/>
       <c r="BU98" s="3"/>
       <c r="BV98" s="3"/>
-    </row>
-    <row r="99" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW98" s="3"/>
+      <c r="BX98" s="3"/>
+    </row>
+    <row r="99" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -15117,8 +15585,10 @@
       <c r="BT99" s="3"/>
       <c r="BU99" s="3"/>
       <c r="BV99" s="3"/>
-    </row>
-    <row r="100" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW99" s="3"/>
+      <c r="BX99" s="3"/>
+    </row>
+    <row r="100" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -15191,8 +15661,10 @@
       <c r="BT100" s="3"/>
       <c r="BU100" s="3"/>
       <c r="BV100" s="3"/>
-    </row>
-    <row r="101" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW100" s="3"/>
+      <c r="BX100" s="3"/>
+    </row>
+    <row r="101" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -15265,8 +15737,10 @@
       <c r="BT101" s="3"/>
       <c r="BU101" s="3"/>
       <c r="BV101" s="3"/>
-    </row>
-    <row r="102" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW101" s="3"/>
+      <c r="BX101" s="3"/>
+    </row>
+    <row r="102" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -15339,8 +15813,10 @@
       <c r="BT102" s="3"/>
       <c r="BU102" s="3"/>
       <c r="BV102" s="3"/>
-    </row>
-    <row r="103" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+    </row>
+    <row r="103" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -15413,8 +15889,10 @@
       <c r="BT103" s="3"/>
       <c r="BU103" s="3"/>
       <c r="BV103" s="3"/>
-    </row>
-    <row r="104" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+    </row>
+    <row r="104" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -15487,8 +15965,10 @@
       <c r="BT104" s="3"/>
       <c r="BU104" s="3"/>
       <c r="BV104" s="3"/>
-    </row>
-    <row r="105" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+    </row>
+    <row r="105" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -15561,8 +16041,10 @@
       <c r="BT105" s="3"/>
       <c r="BU105" s="3"/>
       <c r="BV105" s="3"/>
-    </row>
-    <row r="106" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW105" s="3"/>
+      <c r="BX105" s="3"/>
+    </row>
+    <row r="106" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -15635,8 +16117,10 @@
       <c r="BT106" s="3"/>
       <c r="BU106" s="3"/>
       <c r="BV106" s="3"/>
-    </row>
-    <row r="107" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW106" s="3"/>
+      <c r="BX106" s="3"/>
+    </row>
+    <row r="107" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -15709,8 +16193,10 @@
       <c r="BT107" s="3"/>
       <c r="BU107" s="3"/>
       <c r="BV107" s="3"/>
-    </row>
-    <row r="108" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW107" s="3"/>
+      <c r="BX107" s="3"/>
+    </row>
+    <row r="108" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -15783,8 +16269,10 @@
       <c r="BT108" s="3"/>
       <c r="BU108" s="3"/>
       <c r="BV108" s="3"/>
-    </row>
-    <row r="109" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW108" s="3"/>
+      <c r="BX108" s="3"/>
+    </row>
+    <row r="109" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -15857,8 +16345,10 @@
       <c r="BT109" s="3"/>
       <c r="BU109" s="3"/>
       <c r="BV109" s="3"/>
-    </row>
-    <row r="110" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW109" s="3"/>
+      <c r="BX109" s="3"/>
+    </row>
+    <row r="110" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -15931,8 +16421,10 @@
       <c r="BT110" s="3"/>
       <c r="BU110" s="3"/>
       <c r="BV110" s="3"/>
-    </row>
-    <row r="111" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW110" s="3"/>
+      <c r="BX110" s="3"/>
+    </row>
+    <row r="111" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -16005,8 +16497,10 @@
       <c r="BT111" s="3"/>
       <c r="BU111" s="3"/>
       <c r="BV111" s="3"/>
-    </row>
-    <row r="112" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW111" s="3"/>
+      <c r="BX111" s="3"/>
+    </row>
+    <row r="112" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -16079,8 +16573,10 @@
       <c r="BT112" s="3"/>
       <c r="BU112" s="3"/>
       <c r="BV112" s="3"/>
-    </row>
-    <row r="113" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW112" s="3"/>
+      <c r="BX112" s="3"/>
+    </row>
+    <row r="113" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -16153,8 +16649,10 @@
       <c r="BT113" s="3"/>
       <c r="BU113" s="3"/>
       <c r="BV113" s="3"/>
-    </row>
-    <row r="114" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW113" s="3"/>
+      <c r="BX113" s="3"/>
+    </row>
+    <row r="114" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -16227,8 +16725,10 @@
       <c r="BT114" s="3"/>
       <c r="BU114" s="3"/>
       <c r="BV114" s="3"/>
-    </row>
-    <row r="115" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW114" s="3"/>
+      <c r="BX114" s="3"/>
+    </row>
+    <row r="115" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -16301,8 +16801,10 @@
       <c r="BT115" s="3"/>
       <c r="BU115" s="3"/>
       <c r="BV115" s="3"/>
-    </row>
-    <row r="116" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW115" s="3"/>
+      <c r="BX115" s="3"/>
+    </row>
+    <row r="116" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -16375,8 +16877,10 @@
       <c r="BT116" s="3"/>
       <c r="BU116" s="3"/>
       <c r="BV116" s="3"/>
-    </row>
-    <row r="117" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW116" s="3"/>
+      <c r="BX116" s="3"/>
+    </row>
+    <row r="117" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -16449,8 +16953,10 @@
       <c r="BT117" s="3"/>
       <c r="BU117" s="3"/>
       <c r="BV117" s="3"/>
-    </row>
-    <row r="118" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW117" s="3"/>
+      <c r="BX117" s="3"/>
+    </row>
+    <row r="118" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -16523,8 +17029,10 @@
       <c r="BT118" s="3"/>
       <c r="BU118" s="3"/>
       <c r="BV118" s="3"/>
-    </row>
-    <row r="119" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW118" s="3"/>
+      <c r="BX118" s="3"/>
+    </row>
+    <row r="119" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -16597,8 +17105,10 @@
       <c r="BT119" s="3"/>
       <c r="BU119" s="3"/>
       <c r="BV119" s="3"/>
-    </row>
-    <row r="120" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW119" s="3"/>
+      <c r="BX119" s="3"/>
+    </row>
+    <row r="120" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -16671,8 +17181,10 @@
       <c r="BT120" s="3"/>
       <c r="BU120" s="3"/>
       <c r="BV120" s="3"/>
-    </row>
-    <row r="121" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW120" s="3"/>
+      <c r="BX120" s="3"/>
+    </row>
+    <row r="121" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -16745,8 +17257,10 @@
       <c r="BT121" s="3"/>
       <c r="BU121" s="3"/>
       <c r="BV121" s="3"/>
-    </row>
-    <row r="122" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW121" s="3"/>
+      <c r="BX121" s="3"/>
+    </row>
+    <row r="122" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -16819,8 +17333,10 @@
       <c r="BT122" s="3"/>
       <c r="BU122" s="3"/>
       <c r="BV122" s="3"/>
-    </row>
-    <row r="123" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW122" s="3"/>
+      <c r="BX122" s="3"/>
+    </row>
+    <row r="123" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -16893,8 +17409,10 @@
       <c r="BT123" s="3"/>
       <c r="BU123" s="3"/>
       <c r="BV123" s="3"/>
-    </row>
-    <row r="124" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW123" s="3"/>
+      <c r="BX123" s="3"/>
+    </row>
+    <row r="124" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -16967,8 +17485,10 @@
       <c r="BT124" s="3"/>
       <c r="BU124" s="3"/>
       <c r="BV124" s="3"/>
-    </row>
-    <row r="125" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW124" s="3"/>
+      <c r="BX124" s="3"/>
+    </row>
+    <row r="125" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -17041,8 +17561,10 @@
       <c r="BT125" s="3"/>
       <c r="BU125" s="3"/>
       <c r="BV125" s="3"/>
-    </row>
-    <row r="126" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW125" s="3"/>
+      <c r="BX125" s="3"/>
+    </row>
+    <row r="126" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -17115,8 +17637,10 @@
       <c r="BT126" s="3"/>
       <c r="BU126" s="3"/>
       <c r="BV126" s="3"/>
-    </row>
-    <row r="127" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW126" s="3"/>
+      <c r="BX126" s="3"/>
+    </row>
+    <row r="127" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -17189,8 +17713,10 @@
       <c r="BT127" s="3"/>
       <c r="BU127" s="3"/>
       <c r="BV127" s="3"/>
-    </row>
-    <row r="128" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW127" s="3"/>
+      <c r="BX127" s="3"/>
+    </row>
+    <row r="128" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -17263,8 +17789,10 @@
       <c r="BT128" s="3"/>
       <c r="BU128" s="3"/>
       <c r="BV128" s="3"/>
-    </row>
-    <row r="129" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW128" s="3"/>
+      <c r="BX128" s="3"/>
+    </row>
+    <row r="129" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -17337,8 +17865,10 @@
       <c r="BT129" s="3"/>
       <c r="BU129" s="3"/>
       <c r="BV129" s="3"/>
-    </row>
-    <row r="130" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW129" s="3"/>
+      <c r="BX129" s="3"/>
+    </row>
+    <row r="130" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -17411,8 +17941,10 @@
       <c r="BT130" s="3"/>
       <c r="BU130" s="3"/>
       <c r="BV130" s="3"/>
-    </row>
-    <row r="131" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW130" s="3"/>
+      <c r="BX130" s="3"/>
+    </row>
+    <row r="131" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -17485,8 +18017,10 @@
       <c r="BT131" s="3"/>
       <c r="BU131" s="3"/>
       <c r="BV131" s="3"/>
-    </row>
-    <row r="132" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW131" s="3"/>
+      <c r="BX131" s="3"/>
+    </row>
+    <row r="132" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -17559,8 +18093,10 @@
       <c r="BT132" s="3"/>
       <c r="BU132" s="3"/>
       <c r="BV132" s="3"/>
-    </row>
-    <row r="133" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW132" s="3"/>
+      <c r="BX132" s="3"/>
+    </row>
+    <row r="133" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -17633,8 +18169,10 @@
       <c r="BT133" s="3"/>
       <c r="BU133" s="3"/>
       <c r="BV133" s="3"/>
-    </row>
-    <row r="134" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW133" s="3"/>
+      <c r="BX133" s="3"/>
+    </row>
+    <row r="134" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -17707,8 +18245,10 @@
       <c r="BT134" s="3"/>
       <c r="BU134" s="3"/>
       <c r="BV134" s="3"/>
-    </row>
-    <row r="135" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW134" s="3"/>
+      <c r="BX134" s="3"/>
+    </row>
+    <row r="135" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -17781,8 +18321,10 @@
       <c r="BT135" s="3"/>
       <c r="BU135" s="3"/>
       <c r="BV135" s="3"/>
-    </row>
-    <row r="136" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW135" s="3"/>
+      <c r="BX135" s="3"/>
+    </row>
+    <row r="136" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -17855,8 +18397,10 @@
       <c r="BT136" s="3"/>
       <c r="BU136" s="3"/>
       <c r="BV136" s="3"/>
-    </row>
-    <row r="137" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW136" s="3"/>
+      <c r="BX136" s="3"/>
+    </row>
+    <row r="137" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -17929,8 +18473,10 @@
       <c r="BT137" s="3"/>
       <c r="BU137" s="3"/>
       <c r="BV137" s="3"/>
-    </row>
-    <row r="138" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW137" s="3"/>
+      <c r="BX137" s="3"/>
+    </row>
+    <row r="138" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -18003,8 +18549,10 @@
       <c r="BT138" s="3"/>
       <c r="BU138" s="3"/>
       <c r="BV138" s="3"/>
-    </row>
-    <row r="139" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW138" s="3"/>
+      <c r="BX138" s="3"/>
+    </row>
+    <row r="139" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -18077,8 +18625,10 @@
       <c r="BT139" s="3"/>
       <c r="BU139" s="3"/>
       <c r="BV139" s="3"/>
-    </row>
-    <row r="140" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW139" s="3"/>
+      <c r="BX139" s="3"/>
+    </row>
+    <row r="140" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -18151,8 +18701,10 @@
       <c r="BT140" s="3"/>
       <c r="BU140" s="3"/>
       <c r="BV140" s="3"/>
-    </row>
-    <row r="141" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW140" s="3"/>
+      <c r="BX140" s="3"/>
+    </row>
+    <row r="141" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -18225,8 +18777,10 @@
       <c r="BT141" s="3"/>
       <c r="BU141" s="3"/>
       <c r="BV141" s="3"/>
-    </row>
-    <row r="142" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW141" s="3"/>
+      <c r="BX141" s="3"/>
+    </row>
+    <row r="142" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -18299,8 +18853,10 @@
       <c r="BT142" s="3"/>
       <c r="BU142" s="3"/>
       <c r="BV142" s="3"/>
-    </row>
-    <row r="143" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW142" s="3"/>
+      <c r="BX142" s="3"/>
+    </row>
+    <row r="143" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -18373,8 +18929,10 @@
       <c r="BT143" s="3"/>
       <c r="BU143" s="3"/>
       <c r="BV143" s="3"/>
-    </row>
-    <row r="144" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW143" s="3"/>
+      <c r="BX143" s="3"/>
+    </row>
+    <row r="144" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -18447,8 +19005,10 @@
       <c r="BT144" s="3"/>
       <c r="BU144" s="3"/>
       <c r="BV144" s="3"/>
-    </row>
-    <row r="145" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW144" s="3"/>
+      <c r="BX144" s="3"/>
+    </row>
+    <row r="145" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -18521,8 +19081,10 @@
       <c r="BT145" s="3"/>
       <c r="BU145" s="3"/>
       <c r="BV145" s="3"/>
-    </row>
-    <row r="146" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW145" s="3"/>
+      <c r="BX145" s="3"/>
+    </row>
+    <row r="146" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -18595,8 +19157,10 @@
       <c r="BT146" s="3"/>
       <c r="BU146" s="3"/>
       <c r="BV146" s="3"/>
-    </row>
-    <row r="147" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW146" s="3"/>
+      <c r="BX146" s="3"/>
+    </row>
+    <row r="147" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -18669,8 +19233,10 @@
       <c r="BT147" s="3"/>
       <c r="BU147" s="3"/>
       <c r="BV147" s="3"/>
-    </row>
-    <row r="148" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW147" s="3"/>
+      <c r="BX147" s="3"/>
+    </row>
+    <row r="148" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -18743,8 +19309,10 @@
       <c r="BT148" s="3"/>
       <c r="BU148" s="3"/>
       <c r="BV148" s="3"/>
-    </row>
-    <row r="149" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW148" s="3"/>
+      <c r="BX148" s="3"/>
+    </row>
+    <row r="149" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -18817,8 +19385,10 @@
       <c r="BT149" s="3"/>
       <c r="BU149" s="3"/>
       <c r="BV149" s="3"/>
-    </row>
-    <row r="150" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW149" s="3"/>
+      <c r="BX149" s="3"/>
+    </row>
+    <row r="150" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -18891,8 +19461,10 @@
       <c r="BT150" s="3"/>
       <c r="BU150" s="3"/>
       <c r="BV150" s="3"/>
-    </row>
-    <row r="151" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW150" s="3"/>
+      <c r="BX150" s="3"/>
+    </row>
+    <row r="151" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -18965,8 +19537,10 @@
       <c r="BT151" s="3"/>
       <c r="BU151" s="3"/>
       <c r="BV151" s="3"/>
-    </row>
-    <row r="152" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW151" s="3"/>
+      <c r="BX151" s="3"/>
+    </row>
+    <row r="152" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -19039,8 +19613,10 @@
       <c r="BT152" s="3"/>
       <c r="BU152" s="3"/>
       <c r="BV152" s="3"/>
-    </row>
-    <row r="153" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW152" s="3"/>
+      <c r="BX152" s="3"/>
+    </row>
+    <row r="153" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -19113,8 +19689,10 @@
       <c r="BT153" s="3"/>
       <c r="BU153" s="3"/>
       <c r="BV153" s="3"/>
-    </row>
-    <row r="154" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW153" s="3"/>
+      <c r="BX153" s="3"/>
+    </row>
+    <row r="154" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -19187,8 +19765,10 @@
       <c r="BT154" s="3"/>
       <c r="BU154" s="3"/>
       <c r="BV154" s="3"/>
-    </row>
-    <row r="155" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW154" s="3"/>
+      <c r="BX154" s="3"/>
+    </row>
+    <row r="155" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -19261,8 +19841,10 @@
       <c r="BT155" s="3"/>
       <c r="BU155" s="3"/>
       <c r="BV155" s="3"/>
-    </row>
-    <row r="156" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW155" s="3"/>
+      <c r="BX155" s="3"/>
+    </row>
+    <row r="156" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -19335,8 +19917,10 @@
       <c r="BT156" s="3"/>
       <c r="BU156" s="3"/>
       <c r="BV156" s="3"/>
-    </row>
-    <row r="157" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW156" s="3"/>
+      <c r="BX156" s="3"/>
+    </row>
+    <row r="157" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -19409,8 +19993,10 @@
       <c r="BT157" s="3"/>
       <c r="BU157" s="3"/>
       <c r="BV157" s="3"/>
-    </row>
-    <row r="158" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW157" s="3"/>
+      <c r="BX157" s="3"/>
+    </row>
+    <row r="158" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -19483,8 +20069,10 @@
       <c r="BT158" s="3"/>
       <c r="BU158" s="3"/>
       <c r="BV158" s="3"/>
-    </row>
-    <row r="159" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW158" s="3"/>
+      <c r="BX158" s="3"/>
+    </row>
+    <row r="159" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -19557,8 +20145,10 @@
       <c r="BT159" s="3"/>
       <c r="BU159" s="3"/>
       <c r="BV159" s="3"/>
-    </row>
-    <row r="160" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW159" s="3"/>
+      <c r="BX159" s="3"/>
+    </row>
+    <row r="160" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -19631,8 +20221,10 @@
       <c r="BT160" s="3"/>
       <c r="BU160" s="3"/>
       <c r="BV160" s="3"/>
-    </row>
-    <row r="161" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW160" s="3"/>
+      <c r="BX160" s="3"/>
+    </row>
+    <row r="161" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -19705,8 +20297,10 @@
       <c r="BT161" s="3"/>
       <c r="BU161" s="3"/>
       <c r="BV161" s="3"/>
-    </row>
-    <row r="162" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW161" s="3"/>
+      <c r="BX161" s="3"/>
+    </row>
+    <row r="162" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -19779,8 +20373,10 @@
       <c r="BT162" s="3"/>
       <c r="BU162" s="3"/>
       <c r="BV162" s="3"/>
-    </row>
-    <row r="163" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW162" s="3"/>
+      <c r="BX162" s="3"/>
+    </row>
+    <row r="163" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -19853,8 +20449,10 @@
       <c r="BT163" s="3"/>
       <c r="BU163" s="3"/>
       <c r="BV163" s="3"/>
-    </row>
-    <row r="164" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW163" s="3"/>
+      <c r="BX163" s="3"/>
+    </row>
+    <row r="164" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -19927,8 +20525,10 @@
       <c r="BT164" s="3"/>
       <c r="BU164" s="3"/>
       <c r="BV164" s="3"/>
-    </row>
-    <row r="165" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW164" s="3"/>
+      <c r="BX164" s="3"/>
+    </row>
+    <row r="165" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -20001,8 +20601,10 @@
       <c r="BT165" s="3"/>
       <c r="BU165" s="3"/>
       <c r="BV165" s="3"/>
-    </row>
-    <row r="166" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW165" s="3"/>
+      <c r="BX165" s="3"/>
+    </row>
+    <row r="166" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -20075,8 +20677,10 @@
       <c r="BT166" s="3"/>
       <c r="BU166" s="3"/>
       <c r="BV166" s="3"/>
-    </row>
-    <row r="167" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW166" s="3"/>
+      <c r="BX166" s="3"/>
+    </row>
+    <row r="167" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -20149,8 +20753,10 @@
       <c r="BT167" s="3"/>
       <c r="BU167" s="3"/>
       <c r="BV167" s="3"/>
-    </row>
-    <row r="168" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW167" s="3"/>
+      <c r="BX167" s="3"/>
+    </row>
+    <row r="168" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -20223,8 +20829,10 @@
       <c r="BT168" s="3"/>
       <c r="BU168" s="3"/>
       <c r="BV168" s="3"/>
-    </row>
-    <row r="169" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW168" s="3"/>
+      <c r="BX168" s="3"/>
+    </row>
+    <row r="169" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -20297,8 +20905,10 @@
       <c r="BT169" s="3"/>
       <c r="BU169" s="3"/>
       <c r="BV169" s="3"/>
-    </row>
-    <row r="170" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW169" s="3"/>
+      <c r="BX169" s="3"/>
+    </row>
+    <row r="170" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -20371,8 +20981,10 @@
       <c r="BT170" s="3"/>
       <c r="BU170" s="3"/>
       <c r="BV170" s="3"/>
-    </row>
-    <row r="171" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW170" s="3"/>
+      <c r="BX170" s="3"/>
+    </row>
+    <row r="171" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -20445,8 +21057,10 @@
       <c r="BT171" s="3"/>
       <c r="BU171" s="3"/>
       <c r="BV171" s="3"/>
-    </row>
-    <row r="172" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW171" s="3"/>
+      <c r="BX171" s="3"/>
+    </row>
+    <row r="172" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -20519,8 +21133,10 @@
       <c r="BT172" s="3"/>
       <c r="BU172" s="3"/>
       <c r="BV172" s="3"/>
-    </row>
-    <row r="173" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW172" s="3"/>
+      <c r="BX172" s="3"/>
+    </row>
+    <row r="173" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -20593,8 +21209,10 @@
       <c r="BT173" s="3"/>
       <c r="BU173" s="3"/>
       <c r="BV173" s="3"/>
-    </row>
-    <row r="174" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW173" s="3"/>
+      <c r="BX173" s="3"/>
+    </row>
+    <row r="174" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -20667,8 +21285,10 @@
       <c r="BT174" s="3"/>
       <c r="BU174" s="3"/>
       <c r="BV174" s="3"/>
-    </row>
-    <row r="175" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW174" s="3"/>
+      <c r="BX174" s="3"/>
+    </row>
+    <row r="175" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -20741,8 +21361,10 @@
       <c r="BT175" s="3"/>
       <c r="BU175" s="3"/>
       <c r="BV175" s="3"/>
-    </row>
-    <row r="176" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW175" s="3"/>
+      <c r="BX175" s="3"/>
+    </row>
+    <row r="176" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -20815,8 +21437,10 @@
       <c r="BT176" s="3"/>
       <c r="BU176" s="3"/>
       <c r="BV176" s="3"/>
-    </row>
-    <row r="177" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW176" s="3"/>
+      <c r="BX176" s="3"/>
+    </row>
+    <row r="177" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -20889,8 +21513,10 @@
       <c r="BT177" s="3"/>
       <c r="BU177" s="3"/>
       <c r="BV177" s="3"/>
-    </row>
-    <row r="178" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW177" s="3"/>
+      <c r="BX177" s="3"/>
+    </row>
+    <row r="178" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -20963,8 +21589,10 @@
       <c r="BT178" s="3"/>
       <c r="BU178" s="3"/>
       <c r="BV178" s="3"/>
-    </row>
-    <row r="179" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW178" s="3"/>
+      <c r="BX178" s="3"/>
+    </row>
+    <row r="179" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -21037,8 +21665,10 @@
       <c r="BT179" s="3"/>
       <c r="BU179" s="3"/>
       <c r="BV179" s="3"/>
-    </row>
-    <row r="180" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW179" s="3"/>
+      <c r="BX179" s="3"/>
+    </row>
+    <row r="180" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -21111,8 +21741,10 @@
       <c r="BT180" s="3"/>
       <c r="BU180" s="3"/>
       <c r="BV180" s="3"/>
-    </row>
-    <row r="181" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW180" s="3"/>
+      <c r="BX180" s="3"/>
+    </row>
+    <row r="181" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -21185,8 +21817,10 @@
       <c r="BT181" s="3"/>
       <c r="BU181" s="3"/>
       <c r="BV181" s="3"/>
-    </row>
-    <row r="182" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW181" s="3"/>
+      <c r="BX181" s="3"/>
+    </row>
+    <row r="182" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -21259,8 +21893,10 @@
       <c r="BT182" s="3"/>
       <c r="BU182" s="3"/>
       <c r="BV182" s="3"/>
-    </row>
-    <row r="183" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW182" s="3"/>
+      <c r="BX182" s="3"/>
+    </row>
+    <row r="183" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -21333,8 +21969,10 @@
       <c r="BT183" s="3"/>
       <c r="BU183" s="3"/>
       <c r="BV183" s="3"/>
-    </row>
-    <row r="184" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW183" s="3"/>
+      <c r="BX183" s="3"/>
+    </row>
+    <row r="184" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -21407,8 +22045,10 @@
       <c r="BT184" s="3"/>
       <c r="BU184" s="3"/>
       <c r="BV184" s="3"/>
-    </row>
-    <row r="185" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW184" s="3"/>
+      <c r="BX184" s="3"/>
+    </row>
+    <row r="185" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -21481,8 +22121,10 @@
       <c r="BT185" s="3"/>
       <c r="BU185" s="3"/>
       <c r="BV185" s="3"/>
-    </row>
-    <row r="186" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW185" s="3"/>
+      <c r="BX185" s="3"/>
+    </row>
+    <row r="186" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -21555,8 +22197,10 @@
       <c r="BT186" s="3"/>
       <c r="BU186" s="3"/>
       <c r="BV186" s="3"/>
-    </row>
-    <row r="187" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW186" s="3"/>
+      <c r="BX186" s="3"/>
+    </row>
+    <row r="187" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -21629,8 +22273,10 @@
       <c r="BT187" s="3"/>
       <c r="BU187" s="3"/>
       <c r="BV187" s="3"/>
-    </row>
-    <row r="188" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW187" s="3"/>
+      <c r="BX187" s="3"/>
+    </row>
+    <row r="188" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -21703,8 +22349,10 @@
       <c r="BT188" s="3"/>
       <c r="BU188" s="3"/>
       <c r="BV188" s="3"/>
-    </row>
-    <row r="189" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW188" s="3"/>
+      <c r="BX188" s="3"/>
+    </row>
+    <row r="189" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -21777,8 +22425,10 @@
       <c r="BT189" s="3"/>
       <c r="BU189" s="3"/>
       <c r="BV189" s="3"/>
-    </row>
-    <row r="190" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW189" s="3"/>
+      <c r="BX189" s="3"/>
+    </row>
+    <row r="190" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -21851,8 +22501,10 @@
       <c r="BT190" s="3"/>
       <c r="BU190" s="3"/>
       <c r="BV190" s="3"/>
-    </row>
-    <row r="191" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW190" s="3"/>
+      <c r="BX190" s="3"/>
+    </row>
+    <row r="191" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -21925,8 +22577,10 @@
       <c r="BT191" s="3"/>
       <c r="BU191" s="3"/>
       <c r="BV191" s="3"/>
-    </row>
-    <row r="192" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW191" s="3"/>
+      <c r="BX191" s="3"/>
+    </row>
+    <row r="192" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -21999,8 +22653,10 @@
       <c r="BT192" s="3"/>
       <c r="BU192" s="3"/>
       <c r="BV192" s="3"/>
-    </row>
-    <row r="193" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW192" s="3"/>
+      <c r="BX192" s="3"/>
+    </row>
+    <row r="193" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -22073,8 +22729,10 @@
       <c r="BT193" s="3"/>
       <c r="BU193" s="3"/>
       <c r="BV193" s="3"/>
-    </row>
-    <row r="194" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW193" s="3"/>
+      <c r="BX193" s="3"/>
+    </row>
+    <row r="194" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -22147,8 +22805,10 @@
       <c r="BT194" s="3"/>
       <c r="BU194" s="3"/>
       <c r="BV194" s="3"/>
-    </row>
-    <row r="195" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW194" s="3"/>
+      <c r="BX194" s="3"/>
+    </row>
+    <row r="195" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -22221,8 +22881,10 @@
       <c r="BT195" s="3"/>
       <c r="BU195" s="3"/>
       <c r="BV195" s="3"/>
-    </row>
-    <row r="196" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW195" s="3"/>
+      <c r="BX195" s="3"/>
+    </row>
+    <row r="196" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -22295,8 +22957,10 @@
       <c r="BT196" s="3"/>
       <c r="BU196" s="3"/>
       <c r="BV196" s="3"/>
-    </row>
-    <row r="197" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW196" s="3"/>
+      <c r="BX196" s="3"/>
+    </row>
+    <row r="197" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -22369,8 +23033,10 @@
       <c r="BT197" s="3"/>
       <c r="BU197" s="3"/>
       <c r="BV197" s="3"/>
-    </row>
-    <row r="198" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW197" s="3"/>
+      <c r="BX197" s="3"/>
+    </row>
+    <row r="198" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -22443,8 +23109,10 @@
       <c r="BT198" s="3"/>
       <c r="BU198" s="3"/>
       <c r="BV198" s="3"/>
-    </row>
-    <row r="199" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW198" s="3"/>
+      <c r="BX198" s="3"/>
+    </row>
+    <row r="199" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -22517,8 +23185,10 @@
       <c r="BT199" s="3"/>
       <c r="BU199" s="3"/>
       <c r="BV199" s="3"/>
-    </row>
-    <row r="200" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW199" s="3"/>
+      <c r="BX199" s="3"/>
+    </row>
+    <row r="200" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -22591,8 +23261,10 @@
       <c r="BT200" s="3"/>
       <c r="BU200" s="3"/>
       <c r="BV200" s="3"/>
-    </row>
-    <row r="201" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW200" s="3"/>
+      <c r="BX200" s="3"/>
+    </row>
+    <row r="201" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -22665,8 +23337,10 @@
       <c r="BT201" s="3"/>
       <c r="BU201" s="3"/>
       <c r="BV201" s="3"/>
-    </row>
-    <row r="202" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW201" s="3"/>
+      <c r="BX201" s="3"/>
+    </row>
+    <row r="202" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -22739,8 +23413,10 @@
       <c r="BT202" s="3"/>
       <c r="BU202" s="3"/>
       <c r="BV202" s="3"/>
-    </row>
-    <row r="203" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW202" s="3"/>
+      <c r="BX202" s="3"/>
+    </row>
+    <row r="203" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -22813,8 +23489,10 @@
       <c r="BT203" s="3"/>
       <c r="BU203" s="3"/>
       <c r="BV203" s="3"/>
-    </row>
-    <row r="204" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW203" s="3"/>
+      <c r="BX203" s="3"/>
+    </row>
+    <row r="204" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -22887,8 +23565,10 @@
       <c r="BT204" s="3"/>
       <c r="BU204" s="3"/>
       <c r="BV204" s="3"/>
-    </row>
-    <row r="205" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW204" s="3"/>
+      <c r="BX204" s="3"/>
+    </row>
+    <row r="205" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -22961,8 +23641,10 @@
       <c r="BT205" s="3"/>
       <c r="BU205" s="3"/>
       <c r="BV205" s="3"/>
-    </row>
-    <row r="206" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW205" s="3"/>
+      <c r="BX205" s="3"/>
+    </row>
+    <row r="206" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -23035,8 +23717,10 @@
       <c r="BT206" s="3"/>
       <c r="BU206" s="3"/>
       <c r="BV206" s="3"/>
-    </row>
-    <row r="207" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW206" s="3"/>
+      <c r="BX206" s="3"/>
+    </row>
+    <row r="207" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -23109,8 +23793,10 @@
       <c r="BT207" s="3"/>
       <c r="BU207" s="3"/>
       <c r="BV207" s="3"/>
-    </row>
-    <row r="208" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW207" s="3"/>
+      <c r="BX207" s="3"/>
+    </row>
+    <row r="208" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -23183,8 +23869,10 @@
       <c r="BT208" s="3"/>
       <c r="BU208" s="3"/>
       <c r="BV208" s="3"/>
-    </row>
-    <row r="209" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW208" s="3"/>
+      <c r="BX208" s="3"/>
+    </row>
+    <row r="209" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -23257,8 +23945,10 @@
       <c r="BT209" s="3"/>
       <c r="BU209" s="3"/>
       <c r="BV209" s="3"/>
-    </row>
-    <row r="210" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW209" s="3"/>
+      <c r="BX209" s="3"/>
+    </row>
+    <row r="210" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -23331,8 +24021,10 @@
       <c r="BT210" s="3"/>
       <c r="BU210" s="3"/>
       <c r="BV210" s="3"/>
-    </row>
-    <row r="211" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW210" s="3"/>
+      <c r="BX210" s="3"/>
+    </row>
+    <row r="211" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -23405,8 +24097,10 @@
       <c r="BT211" s="3"/>
       <c r="BU211" s="3"/>
       <c r="BV211" s="3"/>
-    </row>
-    <row r="212" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW211" s="3"/>
+      <c r="BX211" s="3"/>
+    </row>
+    <row r="212" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -23479,8 +24173,10 @@
       <c r="BT212" s="3"/>
       <c r="BU212" s="3"/>
       <c r="BV212" s="3"/>
-    </row>
-    <row r="213" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW212" s="3"/>
+      <c r="BX212" s="3"/>
+    </row>
+    <row r="213" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -23553,8 +24249,10 @@
       <c r="BT213" s="3"/>
       <c r="BU213" s="3"/>
       <c r="BV213" s="3"/>
-    </row>
-    <row r="214" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW213" s="3"/>
+      <c r="BX213" s="3"/>
+    </row>
+    <row r="214" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -23627,8 +24325,10 @@
       <c r="BT214" s="3"/>
       <c r="BU214" s="3"/>
       <c r="BV214" s="3"/>
-    </row>
-    <row r="215" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW214" s="3"/>
+      <c r="BX214" s="3"/>
+    </row>
+    <row r="215" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -23701,8 +24401,10 @@
       <c r="BT215" s="3"/>
       <c r="BU215" s="3"/>
       <c r="BV215" s="3"/>
-    </row>
-    <row r="216" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW215" s="3"/>
+      <c r="BX215" s="3"/>
+    </row>
+    <row r="216" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -23775,8 +24477,10 @@
       <c r="BT216" s="3"/>
       <c r="BU216" s="3"/>
       <c r="BV216" s="3"/>
-    </row>
-    <row r="217" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW216" s="3"/>
+      <c r="BX216" s="3"/>
+    </row>
+    <row r="217" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -23849,8 +24553,10 @@
       <c r="BT217" s="3"/>
       <c r="BU217" s="3"/>
       <c r="BV217" s="3"/>
-    </row>
-    <row r="218" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW217" s="3"/>
+      <c r="BX217" s="3"/>
+    </row>
+    <row r="218" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -23923,8 +24629,10 @@
       <c r="BT218" s="3"/>
       <c r="BU218" s="3"/>
       <c r="BV218" s="3"/>
-    </row>
-    <row r="219" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW218" s="3"/>
+      <c r="BX218" s="3"/>
+    </row>
+    <row r="219" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -23997,8 +24705,10 @@
       <c r="BT219" s="3"/>
       <c r="BU219" s="3"/>
       <c r="BV219" s="3"/>
-    </row>
-    <row r="220" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW219" s="3"/>
+      <c r="BX219" s="3"/>
+    </row>
+    <row r="220" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -24071,8 +24781,10 @@
       <c r="BT220" s="3"/>
       <c r="BU220" s="3"/>
       <c r="BV220" s="3"/>
-    </row>
-    <row r="221" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW220" s="3"/>
+      <c r="BX220" s="3"/>
+    </row>
+    <row r="221" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -24145,8 +24857,10 @@
       <c r="BT221" s="3"/>
       <c r="BU221" s="3"/>
       <c r="BV221" s="3"/>
-    </row>
-    <row r="222" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW221" s="3"/>
+      <c r="BX221" s="3"/>
+    </row>
+    <row r="222" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -24219,8 +24933,10 @@
       <c r="BT222" s="3"/>
       <c r="BU222" s="3"/>
       <c r="BV222" s="3"/>
-    </row>
-    <row r="223" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW222" s="3"/>
+      <c r="BX222" s="3"/>
+    </row>
+    <row r="223" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -24293,8 +25009,10 @@
       <c r="BT223" s="3"/>
       <c r="BU223" s="3"/>
       <c r="BV223" s="3"/>
-    </row>
-    <row r="224" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW223" s="3"/>
+      <c r="BX223" s="3"/>
+    </row>
+    <row r="224" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -24367,8 +25085,10 @@
       <c r="BT224" s="3"/>
       <c r="BU224" s="3"/>
       <c r="BV224" s="3"/>
-    </row>
-    <row r="225" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW224" s="3"/>
+      <c r="BX224" s="3"/>
+    </row>
+    <row r="225" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -24441,8 +25161,10 @@
       <c r="BT225" s="3"/>
       <c r="BU225" s="3"/>
       <c r="BV225" s="3"/>
-    </row>
-    <row r="226" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW225" s="3"/>
+      <c r="BX225" s="3"/>
+    </row>
+    <row r="226" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -24515,8 +25237,10 @@
       <c r="BT226" s="3"/>
       <c r="BU226" s="3"/>
       <c r="BV226" s="3"/>
-    </row>
-    <row r="227" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW226" s="3"/>
+      <c r="BX226" s="3"/>
+    </row>
+    <row r="227" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -24589,8 +25313,10 @@
       <c r="BT227" s="3"/>
       <c r="BU227" s="3"/>
       <c r="BV227" s="3"/>
-    </row>
-    <row r="228" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW227" s="3"/>
+      <c r="BX227" s="3"/>
+    </row>
+    <row r="228" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -24663,8 +25389,10 @@
       <c r="BT228" s="3"/>
       <c r="BU228" s="3"/>
       <c r="BV228" s="3"/>
-    </row>
-    <row r="229" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW228" s="3"/>
+      <c r="BX228" s="3"/>
+    </row>
+    <row r="229" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -24737,8 +25465,10 @@
       <c r="BT229" s="3"/>
       <c r="BU229" s="3"/>
       <c r="BV229" s="3"/>
-    </row>
-    <row r="230" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW229" s="3"/>
+      <c r="BX229" s="3"/>
+    </row>
+    <row r="230" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -24811,8 +25541,10 @@
       <c r="BT230" s="3"/>
       <c r="BU230" s="3"/>
       <c r="BV230" s="3"/>
-    </row>
-    <row r="231" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW230" s="3"/>
+      <c r="BX230" s="3"/>
+    </row>
+    <row r="231" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -24885,8 +25617,10 @@
       <c r="BT231" s="3"/>
       <c r="BU231" s="3"/>
       <c r="BV231" s="3"/>
-    </row>
-    <row r="232" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW231" s="3"/>
+      <c r="BX231" s="3"/>
+    </row>
+    <row r="232" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -24959,8 +25693,10 @@
       <c r="BT232" s="3"/>
       <c r="BU232" s="3"/>
       <c r="BV232" s="3"/>
-    </row>
-    <row r="233" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW232" s="3"/>
+      <c r="BX232" s="3"/>
+    </row>
+    <row r="233" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -25033,8 +25769,10 @@
       <c r="BT233" s="3"/>
       <c r="BU233" s="3"/>
       <c r="BV233" s="3"/>
-    </row>
-    <row r="234" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW233" s="3"/>
+      <c r="BX233" s="3"/>
+    </row>
+    <row r="234" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -25107,8 +25845,10 @@
       <c r="BT234" s="3"/>
       <c r="BU234" s="3"/>
       <c r="BV234" s="3"/>
-    </row>
-    <row r="235" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW234" s="3"/>
+      <c r="BX234" s="3"/>
+    </row>
+    <row r="235" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -25181,8 +25921,10 @@
       <c r="BT235" s="3"/>
       <c r="BU235" s="3"/>
       <c r="BV235" s="3"/>
-    </row>
-    <row r="236" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW235" s="3"/>
+      <c r="BX235" s="3"/>
+    </row>
+    <row r="236" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -25255,8 +25997,10 @@
       <c r="BT236" s="3"/>
       <c r="BU236" s="3"/>
       <c r="BV236" s="3"/>
-    </row>
-    <row r="237" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW236" s="3"/>
+      <c r="BX236" s="3"/>
+    </row>
+    <row r="237" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -25329,8 +26073,10 @@
       <c r="BT237" s="3"/>
       <c r="BU237" s="3"/>
       <c r="BV237" s="3"/>
-    </row>
-    <row r="238" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW237" s="3"/>
+      <c r="BX237" s="3"/>
+    </row>
+    <row r="238" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -25403,8 +26149,10 @@
       <c r="BT238" s="3"/>
       <c r="BU238" s="3"/>
       <c r="BV238" s="3"/>
-    </row>
-    <row r="239" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW238" s="3"/>
+      <c r="BX238" s="3"/>
+    </row>
+    <row r="239" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -25477,8 +26225,10 @@
       <c r="BT239" s="3"/>
       <c r="BU239" s="3"/>
       <c r="BV239" s="3"/>
-    </row>
-    <row r="240" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW239" s="3"/>
+      <c r="BX239" s="3"/>
+    </row>
+    <row r="240" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -25551,8 +26301,10 @@
       <c r="BT240" s="3"/>
       <c r="BU240" s="3"/>
       <c r="BV240" s="3"/>
-    </row>
-    <row r="241" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW240" s="3"/>
+      <c r="BX240" s="3"/>
+    </row>
+    <row r="241" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -25625,8 +26377,10 @@
       <c r="BT241" s="3"/>
       <c r="BU241" s="3"/>
       <c r="BV241" s="3"/>
-    </row>
-    <row r="242" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW241" s="3"/>
+      <c r="BX241" s="3"/>
+    </row>
+    <row r="242" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -25699,8 +26453,10 @@
       <c r="BT242" s="3"/>
       <c r="BU242" s="3"/>
       <c r="BV242" s="3"/>
-    </row>
-    <row r="243" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW242" s="3"/>
+      <c r="BX242" s="3"/>
+    </row>
+    <row r="243" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -25773,8 +26529,10 @@
       <c r="BT243" s="3"/>
       <c r="BU243" s="3"/>
       <c r="BV243" s="3"/>
-    </row>
-    <row r="244" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW243" s="3"/>
+      <c r="BX243" s="3"/>
+    </row>
+    <row r="244" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -25847,8 +26605,10 @@
       <c r="BT244" s="3"/>
       <c r="BU244" s="3"/>
       <c r="BV244" s="3"/>
-    </row>
-    <row r="245" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW244" s="3"/>
+      <c r="BX244" s="3"/>
+    </row>
+    <row r="245" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -25921,8 +26681,10 @@
       <c r="BT245" s="3"/>
       <c r="BU245" s="3"/>
       <c r="BV245" s="3"/>
-    </row>
-    <row r="246" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW245" s="3"/>
+      <c r="BX245" s="3"/>
+    </row>
+    <row r="246" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -25995,8 +26757,10 @@
       <c r="BT246" s="3"/>
       <c r="BU246" s="3"/>
       <c r="BV246" s="3"/>
-    </row>
-    <row r="247" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW246" s="3"/>
+      <c r="BX246" s="3"/>
+    </row>
+    <row r="247" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -26069,8 +26833,10 @@
       <c r="BT247" s="3"/>
       <c r="BU247" s="3"/>
       <c r="BV247" s="3"/>
-    </row>
-    <row r="248" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW247" s="3"/>
+      <c r="BX247" s="3"/>
+    </row>
+    <row r="248" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -26143,8 +26909,10 @@
       <c r="BT248" s="3"/>
       <c r="BU248" s="3"/>
       <c r="BV248" s="3"/>
-    </row>
-    <row r="249" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW248" s="3"/>
+      <c r="BX248" s="3"/>
+    </row>
+    <row r="249" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -26217,8 +26985,10 @@
       <c r="BT249" s="3"/>
       <c r="BU249" s="3"/>
       <c r="BV249" s="3"/>
-    </row>
-    <row r="250" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW249" s="3"/>
+      <c r="BX249" s="3"/>
+    </row>
+    <row r="250" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -26291,8 +27061,10 @@
       <c r="BT250" s="3"/>
       <c r="BU250" s="3"/>
       <c r="BV250" s="3"/>
-    </row>
-    <row r="251" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW250" s="3"/>
+      <c r="BX250" s="3"/>
+    </row>
+    <row r="251" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -26365,8 +27137,10 @@
       <c r="BT251" s="3"/>
       <c r="BU251" s="3"/>
       <c r="BV251" s="3"/>
-    </row>
-    <row r="252" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW251" s="3"/>
+      <c r="BX251" s="3"/>
+    </row>
+    <row r="252" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -26439,8 +27213,10 @@
       <c r="BT252" s="3"/>
       <c r="BU252" s="3"/>
       <c r="BV252" s="3"/>
-    </row>
-    <row r="253" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW252" s="3"/>
+      <c r="BX252" s="3"/>
+    </row>
+    <row r="253" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -26513,8 +27289,10 @@
       <c r="BT253" s="3"/>
       <c r="BU253" s="3"/>
       <c r="BV253" s="3"/>
-    </row>
-    <row r="254" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW253" s="3"/>
+      <c r="BX253" s="3"/>
+    </row>
+    <row r="254" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -26587,8 +27365,10 @@
       <c r="BT254" s="3"/>
       <c r="BU254" s="3"/>
       <c r="BV254" s="3"/>
-    </row>
-    <row r="255" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW254" s="3"/>
+      <c r="BX254" s="3"/>
+    </row>
+    <row r="255" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -26661,8 +27441,10 @@
       <c r="BT255" s="3"/>
       <c r="BU255" s="3"/>
       <c r="BV255" s="3"/>
-    </row>
-    <row r="256" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW255" s="3"/>
+      <c r="BX255" s="3"/>
+    </row>
+    <row r="256" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -26735,8 +27517,10 @@
       <c r="BT256" s="3"/>
       <c r="BU256" s="3"/>
       <c r="BV256" s="3"/>
-    </row>
-    <row r="257" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW256" s="3"/>
+      <c r="BX256" s="3"/>
+    </row>
+    <row r="257" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -26809,8 +27593,10 @@
       <c r="BT257" s="3"/>
       <c r="BU257" s="3"/>
       <c r="BV257" s="3"/>
-    </row>
-    <row r="258" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW257" s="3"/>
+      <c r="BX257" s="3"/>
+    </row>
+    <row r="258" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -26883,8 +27669,10 @@
       <c r="BT258" s="3"/>
       <c r="BU258" s="3"/>
       <c r="BV258" s="3"/>
-    </row>
-    <row r="259" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW258" s="3"/>
+      <c r="BX258" s="3"/>
+    </row>
+    <row r="259" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -26957,8 +27745,10 @@
       <c r="BT259" s="3"/>
       <c r="BU259" s="3"/>
       <c r="BV259" s="3"/>
-    </row>
-    <row r="260" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW259" s="3"/>
+      <c r="BX259" s="3"/>
+    </row>
+    <row r="260" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -27031,8 +27821,10 @@
       <c r="BT260" s="3"/>
       <c r="BU260" s="3"/>
       <c r="BV260" s="3"/>
-    </row>
-    <row r="261" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW260" s="3"/>
+      <c r="BX260" s="3"/>
+    </row>
+    <row r="261" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -27105,8 +27897,10 @@
       <c r="BT261" s="3"/>
       <c r="BU261" s="3"/>
       <c r="BV261" s="3"/>
-    </row>
-    <row r="262" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW261" s="3"/>
+      <c r="BX261" s="3"/>
+    </row>
+    <row r="262" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -27179,8 +27973,10 @@
       <c r="BT262" s="3"/>
       <c r="BU262" s="3"/>
       <c r="BV262" s="3"/>
-    </row>
-    <row r="263" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW262" s="3"/>
+      <c r="BX262" s="3"/>
+    </row>
+    <row r="263" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -27253,8 +28049,10 @@
       <c r="BT263" s="3"/>
       <c r="BU263" s="3"/>
       <c r="BV263" s="3"/>
-    </row>
-    <row r="264" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW263" s="3"/>
+      <c r="BX263" s="3"/>
+    </row>
+    <row r="264" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -27327,8 +28125,10 @@
       <c r="BT264" s="3"/>
       <c r="BU264" s="3"/>
       <c r="BV264" s="3"/>
-    </row>
-    <row r="265" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW264" s="3"/>
+      <c r="BX264" s="3"/>
+    </row>
+    <row r="265" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -27401,8 +28201,10 @@
       <c r="BT265" s="3"/>
       <c r="BU265" s="3"/>
       <c r="BV265" s="3"/>
-    </row>
-    <row r="266" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW265" s="3"/>
+      <c r="BX265" s="3"/>
+    </row>
+    <row r="266" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -27475,8 +28277,10 @@
       <c r="BT266" s="3"/>
       <c r="BU266" s="3"/>
       <c r="BV266" s="3"/>
-    </row>
-    <row r="267" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW266" s="3"/>
+      <c r="BX266" s="3"/>
+    </row>
+    <row r="267" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -27549,8 +28353,10 @@
       <c r="BT267" s="3"/>
       <c r="BU267" s="3"/>
       <c r="BV267" s="3"/>
-    </row>
-    <row r="268" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW267" s="3"/>
+      <c r="BX267" s="3"/>
+    </row>
+    <row r="268" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -27623,8 +28429,10 @@
       <c r="BT268" s="3"/>
       <c r="BU268" s="3"/>
       <c r="BV268" s="3"/>
-    </row>
-    <row r="269" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW268" s="3"/>
+      <c r="BX268" s="3"/>
+    </row>
+    <row r="269" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -27697,8 +28505,10 @@
       <c r="BT269" s="3"/>
       <c r="BU269" s="3"/>
       <c r="BV269" s="3"/>
-    </row>
-    <row r="270" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW269" s="3"/>
+      <c r="BX269" s="3"/>
+    </row>
+    <row r="270" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -27771,8 +28581,10 @@
       <c r="BT270" s="3"/>
       <c r="BU270" s="3"/>
       <c r="BV270" s="3"/>
-    </row>
-    <row r="271" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW270" s="3"/>
+      <c r="BX270" s="3"/>
+    </row>
+    <row r="271" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -27845,8 +28657,10 @@
       <c r="BT271" s="3"/>
       <c r="BU271" s="3"/>
       <c r="BV271" s="3"/>
-    </row>
-    <row r="272" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW271" s="3"/>
+      <c r="BX271" s="3"/>
+    </row>
+    <row r="272" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -27919,8 +28733,10 @@
       <c r="BT272" s="3"/>
       <c r="BU272" s="3"/>
       <c r="BV272" s="3"/>
-    </row>
-    <row r="273" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW272" s="3"/>
+      <c r="BX272" s="3"/>
+    </row>
+    <row r="273" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -27993,8 +28809,10 @@
       <c r="BT273" s="3"/>
       <c r="BU273" s="3"/>
       <c r="BV273" s="3"/>
-    </row>
-    <row r="274" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW273" s="3"/>
+      <c r="BX273" s="3"/>
+    </row>
+    <row r="274" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -28067,8 +28885,10 @@
       <c r="BT274" s="3"/>
       <c r="BU274" s="3"/>
       <c r="BV274" s="3"/>
-    </row>
-    <row r="275" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW274" s="3"/>
+      <c r="BX274" s="3"/>
+    </row>
+    <row r="275" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -28141,8 +28961,10 @@
       <c r="BT275" s="3"/>
       <c r="BU275" s="3"/>
       <c r="BV275" s="3"/>
-    </row>
-    <row r="276" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW275" s="3"/>
+      <c r="BX275" s="3"/>
+    </row>
+    <row r="276" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -28215,8 +29037,10 @@
       <c r="BT276" s="3"/>
       <c r="BU276" s="3"/>
       <c r="BV276" s="3"/>
-    </row>
-    <row r="277" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW276" s="3"/>
+      <c r="BX276" s="3"/>
+    </row>
+    <row r="277" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -28289,8 +29113,10 @@
       <c r="BT277" s="3"/>
       <c r="BU277" s="3"/>
       <c r="BV277" s="3"/>
-    </row>
-    <row r="278" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW277" s="3"/>
+      <c r="BX277" s="3"/>
+    </row>
+    <row r="278" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -28363,8 +29189,10 @@
       <c r="BT278" s="3"/>
       <c r="BU278" s="3"/>
       <c r="BV278" s="3"/>
-    </row>
-    <row r="279" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW278" s="3"/>
+      <c r="BX278" s="3"/>
+    </row>
+    <row r="279" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -28437,8 +29265,10 @@
       <c r="BT279" s="3"/>
       <c r="BU279" s="3"/>
       <c r="BV279" s="3"/>
-    </row>
-    <row r="280" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW279" s="3"/>
+      <c r="BX279" s="3"/>
+    </row>
+    <row r="280" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -28511,8 +29341,10 @@
       <c r="BT280" s="3"/>
       <c r="BU280" s="3"/>
       <c r="BV280" s="3"/>
-    </row>
-    <row r="281" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW280" s="3"/>
+      <c r="BX280" s="3"/>
+    </row>
+    <row r="281" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -28585,8 +29417,10 @@
       <c r="BT281" s="3"/>
       <c r="BU281" s="3"/>
       <c r="BV281" s="3"/>
-    </row>
-    <row r="282" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW281" s="3"/>
+      <c r="BX281" s="3"/>
+    </row>
+    <row r="282" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -28659,8 +29493,10 @@
       <c r="BT282" s="3"/>
       <c r="BU282" s="3"/>
       <c r="BV282" s="3"/>
-    </row>
-    <row r="283" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW282" s="3"/>
+      <c r="BX282" s="3"/>
+    </row>
+    <row r="283" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -28733,8 +29569,10 @@
       <c r="BT283" s="3"/>
       <c r="BU283" s="3"/>
       <c r="BV283" s="3"/>
-    </row>
-    <row r="284" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW283" s="3"/>
+      <c r="BX283" s="3"/>
+    </row>
+    <row r="284" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -28807,8 +29645,10 @@
       <c r="BT284" s="3"/>
       <c r="BU284" s="3"/>
       <c r="BV284" s="3"/>
-    </row>
-    <row r="285" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW284" s="3"/>
+      <c r="BX284" s="3"/>
+    </row>
+    <row r="285" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -28881,8 +29721,10 @@
       <c r="BT285" s="3"/>
       <c r="BU285" s="3"/>
       <c r="BV285" s="3"/>
-    </row>
-    <row r="286" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW285" s="3"/>
+      <c r="BX285" s="3"/>
+    </row>
+    <row r="286" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -28955,8 +29797,10 @@
       <c r="BT286" s="3"/>
       <c r="BU286" s="3"/>
       <c r="BV286" s="3"/>
-    </row>
-    <row r="287" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW286" s="3"/>
+      <c r="BX286" s="3"/>
+    </row>
+    <row r="287" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -29029,8 +29873,10 @@
       <c r="BT287" s="3"/>
       <c r="BU287" s="3"/>
       <c r="BV287" s="3"/>
-    </row>
-    <row r="288" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW287" s="3"/>
+      <c r="BX287" s="3"/>
+    </row>
+    <row r="288" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -29103,8 +29949,10 @@
       <c r="BT288" s="3"/>
       <c r="BU288" s="3"/>
       <c r="BV288" s="3"/>
-    </row>
-    <row r="289" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW288" s="3"/>
+      <c r="BX288" s="3"/>
+    </row>
+    <row r="289" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -29177,8 +30025,10 @@
       <c r="BT289" s="3"/>
       <c r="BU289" s="3"/>
       <c r="BV289" s="3"/>
-    </row>
-    <row r="290" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW289" s="3"/>
+      <c r="BX289" s="3"/>
+    </row>
+    <row r="290" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -29251,8 +30101,10 @@
       <c r="BT290" s="3"/>
       <c r="BU290" s="3"/>
       <c r="BV290" s="3"/>
-    </row>
-    <row r="291" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW290" s="3"/>
+      <c r="BX290" s="3"/>
+    </row>
+    <row r="291" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -29325,8 +30177,10 @@
       <c r="BT291" s="3"/>
       <c r="BU291" s="3"/>
       <c r="BV291" s="3"/>
-    </row>
-    <row r="292" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW291" s="3"/>
+      <c r="BX291" s="3"/>
+    </row>
+    <row r="292" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -29399,8 +30253,10 @@
       <c r="BT292" s="3"/>
       <c r="BU292" s="3"/>
       <c r="BV292" s="3"/>
-    </row>
-    <row r="293" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW292" s="3"/>
+      <c r="BX292" s="3"/>
+    </row>
+    <row r="293" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -29473,8 +30329,10 @@
       <c r="BT293" s="3"/>
       <c r="BU293" s="3"/>
       <c r="BV293" s="3"/>
-    </row>
-    <row r="294" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW293" s="3"/>
+      <c r="BX293" s="3"/>
+    </row>
+    <row r="294" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -29547,8 +30405,10 @@
       <c r="BT294" s="3"/>
       <c r="BU294" s="3"/>
       <c r="BV294" s="3"/>
-    </row>
-    <row r="295" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW294" s="3"/>
+      <c r="BX294" s="3"/>
+    </row>
+    <row r="295" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -29621,8 +30481,10 @@
       <c r="BT295" s="3"/>
       <c r="BU295" s="3"/>
       <c r="BV295" s="3"/>
-    </row>
-    <row r="296" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW295" s="3"/>
+      <c r="BX295" s="3"/>
+    </row>
+    <row r="296" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -29695,8 +30557,10 @@
       <c r="BT296" s="3"/>
       <c r="BU296" s="3"/>
       <c r="BV296" s="3"/>
-    </row>
-    <row r="297" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW296" s="3"/>
+      <c r="BX296" s="3"/>
+    </row>
+    <row r="297" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -29769,8 +30633,10 @@
       <c r="BT297" s="3"/>
       <c r="BU297" s="3"/>
       <c r="BV297" s="3"/>
-    </row>
-    <row r="298" spans="3:74" x14ac:dyDescent="0.2">
+      <c r="BW297" s="3"/>
+      <c r="BX297" s="3"/>
+    </row>
+    <row r="298" spans="3:76" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -29843,6 +30709,8 @@
       <c r="BT298" s="3"/>
       <c r="BU298" s="3"/>
       <c r="BV298" s="3"/>
+      <c r="BW298" s="3"/>
+      <c r="BX298" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/CFR.SW.xlsx
+++ b/CFR.SW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD11F2E-81E1-41DC-A2FB-A45662724ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672AD6A-48A6-41CE-991B-5827E7676FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="2" xr2:uid="{F1691F7E-D160-4792-AE06-DE8123BA55BD}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="98">
   <si>
     <t>CFR.SW</t>
   </si>
@@ -328,7 +328,10 @@
     <t>H226</t>
   </si>
   <si>
-    <t>FQ226</t>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -338,13 +341,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -422,28 +431,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -803,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="J2" s="2">
-        <v>138.30000000000001</v>
+        <v>157.35</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -812,7 +824,7 @@
       </c>
       <c r="J3" s="3">
         <f>+J2*J10</f>
-        <v>146.59800000000001</v>
+        <v>166.791</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -822,11 +834,11 @@
       <c r="I4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="5">
-        <v>587.6</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>96</v>
+      <c r="J4" s="3">
+        <v>587.9</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -838,7 +850,7 @@
       </c>
       <c r="J5" s="3">
         <f>+J3*J4</f>
-        <v>86140.984800000006</v>
+        <v>98056.428899999999</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -846,10 +858,10 @@
         <v>5</v>
       </c>
       <c r="J6" s="3">
-        <v>7278</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>96</v>
+        <v>8522</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -857,11 +869,11 @@
         <v>6</v>
       </c>
       <c r="J7" s="3">
-        <f>4486+1502</f>
-        <v>5988</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>96</v>
+        <f>4487+3+4249</f>
+        <v>8739</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -870,7 +882,7 @@
       </c>
       <c r="J8" s="3">
         <f>+J5-J6+J7</f>
-        <v>84850.984800000006</v>
+        <v>98273.428899999999</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -7437,6 +7449,9 @@
       <c r="S2" s="6" t="s">
         <v>69</v>
       </c>
+      <c r="T2" s="15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="3" spans="1:76" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -7479,7 +7494,9 @@
       <c r="S3" s="3">
         <v>4898</v>
       </c>
-      <c r="T3" s="3"/>
+      <c r="T3" s="3">
+        <v>5264</v>
+      </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -7535,7 +7552,9 @@
       <c r="S4" s="3">
         <v>7150</v>
       </c>
-      <c r="T4" s="3"/>
+      <c r="T4" s="3">
+        <v>7204</v>
+      </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -7591,7 +7610,9 @@
       <c r="S5" s="3">
         <v>5236</v>
       </c>
-      <c r="T5" s="3"/>
+      <c r="T5" s="3">
+        <v>5680</v>
+      </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -7647,7 +7668,9 @@
       <c r="S6" s="3">
         <v>2186</v>
       </c>
-      <c r="T6" s="3"/>
+      <c r="T6" s="3">
+        <v>2229</v>
+      </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -7703,7 +7726,9 @@
       <c r="S7" s="3">
         <v>1929</v>
       </c>
-      <c r="T7" s="3"/>
+      <c r="T7" s="3">
+        <v>2043</v>
+      </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -7759,7 +7784,9 @@
       <c r="S8" s="3">
         <v>11476</v>
       </c>
-      <c r="T8" s="3"/>
+      <c r="T8" s="3">
+        <v>12206</v>
+      </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -7815,7 +7842,9 @@
       <c r="S9" s="3">
         <v>6815</v>
       </c>
-      <c r="T9" s="3"/>
+      <c r="T9" s="3">
+        <v>7157</v>
+      </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -7871,7 +7900,9 @@
       <c r="S10" s="3">
         <v>1088</v>
       </c>
-      <c r="T10" s="3"/>
+      <c r="T10" s="3">
+        <v>1002</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -7927,7 +7958,9 @@
       <c r="S11" s="3">
         <v>870</v>
       </c>
-      <c r="T11" s="3"/>
+      <c r="T11" s="3">
+        <v>926</v>
+      </c>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -7983,7 +8016,9 @@
       <c r="S12" s="3">
         <v>427</v>
       </c>
-      <c r="T12" s="3"/>
+      <c r="T12" s="3">
+        <v>415</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -8039,7 +8074,9 @@
       <c r="S13" s="3">
         <v>723</v>
       </c>
-      <c r="T13" s="3"/>
+      <c r="T13" s="3">
+        <v>714</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -8138,7 +8175,9 @@
       <c r="S14" s="3">
         <v>15040</v>
       </c>
-      <c r="T14" s="3"/>
+      <c r="T14" s="3">
+        <v>15847</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -8237,7 +8276,9 @@
       <c r="S15" s="3">
         <v>1355</v>
       </c>
-      <c r="T15" s="3"/>
+      <c r="T15" s="3">
+        <v>1382</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -8336,7 +8377,9 @@
       <c r="S16" s="3">
         <v>5004</v>
       </c>
-      <c r="T16" s="3"/>
+      <c r="T16" s="3">
+        <v>5191</v>
+      </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -8435,7 +8478,9 @@
       <c r="S17" s="10">
         <v>21399</v>
       </c>
-      <c r="T17" s="3"/>
+      <c r="T17" s="10">
+        <v>22420</v>
+      </c>
       <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -8534,7 +8579,9 @@
       <c r="S18" s="3">
         <v>7080</v>
       </c>
-      <c r="T18" s="3"/>
+      <c r="T18" s="3">
+        <v>7982</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -8655,7 +8702,10 @@
         <f>+S17-S18</f>
         <v>14319</v>
       </c>
-      <c r="T19" s="3"/>
+      <c r="T19" s="3">
+        <f>+T17-T18</f>
+        <v>14438</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -8754,7 +8804,9 @@
       <c r="S20" s="3">
         <v>5631</v>
       </c>
-      <c r="T20" s="3"/>
+      <c r="T20" s="3">
+        <v>5731</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -8853,7 +8905,9 @@
       <c r="S21" s="3">
         <v>2093</v>
       </c>
-      <c r="T21" s="3"/>
+      <c r="T21" s="3">
+        <v>1996</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -8952,7 +9006,9 @@
       <c r="S22" s="3">
         <v>1991</v>
       </c>
-      <c r="T22" s="3"/>
+      <c r="T22" s="3">
+        <v>2012</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -9053,7 +9109,9 @@
       <c r="S23" s="3">
         <v>137</v>
       </c>
-      <c r="T23" s="3"/>
+      <c r="T23" s="3">
+        <v>207</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -9144,7 +9202,7 @@
         <v>2206</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:S24" si="6">+J19-SUM(J20:J23)</f>
+        <f t="shared" ref="J24:T24" si="6">+J19-SUM(J20:J23)</f>
         <v>2261</v>
       </c>
       <c r="K24" s="3">
@@ -9177,7 +9235,10 @@
         <f t="shared" si="6"/>
         <v>4467</v>
       </c>
-      <c r="T24" s="3"/>
+      <c r="T24" s="3">
+        <f t="shared" si="6"/>
+        <v>4492</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -9276,7 +9337,9 @@
       <c r="S25" s="3">
         <v>792</v>
       </c>
-      <c r="T25" s="3"/>
+      <c r="T25" s="3">
+        <v>857</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -9375,7 +9438,9 @@
       <c r="S26" s="3">
         <v>739</v>
       </c>
-      <c r="T26" s="3"/>
+      <c r="T26" s="3">
+        <v>713</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -9474,7 +9539,9 @@
       <c r="S27" s="3">
         <v>75</v>
       </c>
-      <c r="T27" s="3"/>
+      <c r="T27" s="3">
+        <v>2</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -9565,7 +9632,7 @@
         <v>2091</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28:S28" si="8">+J24-J25+J26+J27</f>
+        <f t="shared" ref="J28:T28" si="8">+J24-J25+J26+J27</f>
         <v>2398</v>
       </c>
       <c r="K28" s="3">
@@ -9598,7 +9665,10 @@
         <f t="shared" si="8"/>
         <v>4489</v>
       </c>
-      <c r="T28" s="3"/>
+      <c r="T28" s="3">
+        <f t="shared" si="8"/>
+        <v>4350</v>
+      </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -9697,7 +9767,9 @@
       <c r="S29" s="3">
         <v>727</v>
       </c>
-      <c r="T29" s="3"/>
+      <c r="T29" s="3">
+        <v>886</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -9815,7 +9887,10 @@
         <f>+S28-S29</f>
         <v>3762</v>
       </c>
-      <c r="T30" s="3"/>
+      <c r="T30" s="3">
+        <f>+T28-T29</f>
+        <v>3464</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -9914,7 +9989,9 @@
       <c r="S31" s="3">
         <v>1012</v>
       </c>
-      <c r="T31" s="3"/>
+      <c r="T31" s="3">
+        <v>-20</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -10035,7 +10112,10 @@
         <f>+S30-S31</f>
         <v>2750</v>
       </c>
-      <c r="T32" s="3"/>
+      <c r="T32" s="3">
+        <f>+T30-T31</f>
+        <v>3484</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -10235,7 +10315,10 @@
         <f>+S32/S35</f>
         <v>4.6872336799045504</v>
       </c>
-      <c r="T34" s="3"/>
+      <c r="T34" s="13">
+        <f>+T32/T35</f>
+        <v>5.9261779214152073</v>
+      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -10330,7 +10413,9 @@
       <c r="S35" s="5">
         <v>586.70000000000005</v>
       </c>
-      <c r="T35" s="3"/>
+      <c r="T35" s="3">
+        <v>587.9</v>
+      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -10509,7 +10594,10 @@
         <f>+S8/R8-1</f>
         <v>7.2122571001494773E-2</v>
       </c>
-      <c r="T37" s="3"/>
+      <c r="T37" s="11">
+        <f>+T8/S8-1</f>
+        <v>6.3611014290693602E-2</v>
+      </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -10605,14 +10693,17 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="11">
-        <f t="shared" ref="R38:S42" si="20">+R9/Q9-1</f>
+        <f t="shared" ref="R38:T42" si="20">+R9/Q9-1</f>
         <v>2.5776886724904191E-3</v>
       </c>
       <c r="S38" s="11">
         <f t="shared" si="20"/>
         <v>-2.6567633195257789E-2</v>
       </c>
-      <c r="T38" s="3"/>
+      <c r="T38" s="11">
+        <f t="shared" si="20"/>
+        <v>5.018341892883349E-2</v>
+      </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -10715,7 +10806,10 @@
         <f t="shared" si="20"/>
         <v>6.1463414634146396E-2</v>
       </c>
-      <c r="T39" s="3"/>
+      <c r="T39" s="11">
+        <f t="shared" si="20"/>
+        <v>-7.9044117647058876E-2</v>
+      </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -10818,7 +10912,10 @@
         <f t="shared" si="20"/>
         <v>0.10266159695817501</v>
       </c>
-      <c r="T40" s="3"/>
+      <c r="T40" s="11">
+        <f t="shared" si="20"/>
+        <v>6.4367816091954078E-2</v>
+      </c>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -10921,7 +11018,10 @@
         <f t="shared" si="20"/>
         <v>-1.8390804597701149E-2</v>
       </c>
-      <c r="T41" s="3"/>
+      <c r="T41" s="11">
+        <f t="shared" si="20"/>
+        <v>-2.8103044496487151E-2</v>
+      </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -11024,7 +11124,10 @@
         <f t="shared" si="20"/>
         <v>9.2145015105740136E-2</v>
       </c>
-      <c r="T42" s="3"/>
+      <c r="T42" s="11">
+        <f t="shared" si="20"/>
+        <v>-1.2448132780082943E-2</v>
+      </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -11130,7 +11233,10 @@
         <f>+S17/R17-1</f>
         <v>3.7980209545983801E-2</v>
       </c>
-      <c r="T43" s="3"/>
+      <c r="T43" s="12">
+        <f>+T17/S17-1</f>
+        <v>4.7712509930370572E-2</v>
+      </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -11254,7 +11360,10 @@
         <f t="shared" si="26"/>
         <v>0.66914341791672505</v>
       </c>
-      <c r="T44" s="3"/>
+      <c r="T44" s="11">
+        <f t="shared" ref="T44" si="28">+T19/T17</f>
+        <v>0.64397859054415696</v>
+      </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -11317,27 +11426,27 @@
         <v>52</v>
       </c>
       <c r="C45" s="11" t="e">
-        <f t="shared" ref="C45:H45" si="28">+C24/C17</f>
+        <f t="shared" ref="C45:H45" si="29">+C24/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D45" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E45" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F45" s="11" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.25975931904901672</v>
       </c>
       <c r="H45" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.20577200577200577</v>
       </c>
       <c r="I45" s="11">
@@ -11345,40 +11454,43 @@
         <v>0.21891435943237075</v>
       </c>
       <c r="J45" s="11">
-        <f t="shared" ref="J45:S45" si="29">+J24/J17</f>
+        <f t="shared" ref="J45:S45" si="30">+J24/J17</f>
         <v>0.1996996996996997</v>
       </c>
       <c r="K45" s="11">
-        <f t="shared" ref="K45" si="30">+K24/K17</f>
+        <f t="shared" ref="K45" si="31">+K24/K17</f>
         <v>0.22205480742066108</v>
       </c>
       <c r="L45" s="11"/>
       <c r="M45" s="3"/>
       <c r="N45" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O45" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.22408645808454741</v>
       </c>
       <c r="Q45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.25214253495714928</v>
       </c>
       <c r="R45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.23253783469150174</v>
       </c>
       <c r="S45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.20874807233982898</v>
       </c>
-      <c r="T45" s="3"/>
+      <c r="T45" s="11">
+        <f t="shared" ref="T45" si="32">+T24/T17</f>
+        <v>0.20035682426404997</v>
+      </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -11441,27 +11553,27 @@
         <v>53</v>
       </c>
       <c r="C46" s="11" t="e">
-        <f t="shared" ref="C46:H46" si="31">+C29/C28</f>
+        <f t="shared" ref="C46:H46" si="33">+C29/C28</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="11" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="11" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F46" s="11" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.1783948269303918</v>
       </c>
       <c r="H46" s="11">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.18163869693978282</v>
       </c>
       <c r="I46" s="11">
@@ -11469,40 +11581,43 @@
         <v>0.17312290769966523</v>
       </c>
       <c r="J46" s="11">
-        <f t="shared" ref="J46:S46" si="32">+J29/J28</f>
+        <f t="shared" ref="J46:S46" si="34">+J29/J28</f>
         <v>0.15221017514595497</v>
       </c>
       <c r="K46" s="11">
-        <f t="shared" ref="K46" si="33">+K29/K28</f>
+        <f t="shared" ref="K46" si="35">+K29/K28</f>
         <v>0.19244604316546762</v>
       </c>
       <c r="L46" s="11"/>
       <c r="M46" s="3"/>
       <c r="N46" s="11" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O46" s="11" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P46" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.16785592932381924</v>
       </c>
       <c r="Q46" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.17801597309794032</v>
       </c>
       <c r="R46" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.17980665950590763</v>
       </c>
       <c r="S46" s="11">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.16195143684562263</v>
       </c>
-      <c r="T46" s="3"/>
+      <c r="T46" s="11">
+        <f t="shared" ref="T46" si="36">+T29/T28</f>
+        <v>0.20367816091954022</v>
+      </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>

--- a/CFR.SW.xlsx
+++ b/CFR.SW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7672AD6A-48A6-41CE-991B-5827E7676FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC04491-9AB1-47B2-A98E-3D08505E81B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="2" xr2:uid="{F1691F7E-D160-4792-AE06-DE8123BA55BD}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{F1691F7E-D160-4792-AE06-DE8123BA55BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="99">
   <si>
     <t>CFR.SW</t>
   </si>
@@ -333,6 +333,9 @@
   <si>
     <t>FQ426</t>
   </si>
+  <si>
+    <t>Q127</t>
+  </si>
 </sst>
 </file>
 
@@ -341,13 +344,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -431,28 +440,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -999,6 +1011,9 @@
       <c r="J2" s="6" t="s">
         <v>85</v>
       </c>
+      <c r="K2" s="16" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1015,12 +1030,17 @@
       <c r="G3" s="3">
         <v>1295</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <f>+Model!K3-Quartr!G3</f>
+        <v>1291</v>
+      </c>
       <c r="I3" s="3">
         <v>1550</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>1429</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -1059,12 +1079,17 @@
       <c r="G4" s="3">
         <v>1731</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3">
+        <f>+Model!K4-Quartr!G4</f>
+        <v>1710</v>
+      </c>
       <c r="I4" s="3">
         <v>1870</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>2068</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1103,12 +1128,17 @@
       <c r="G5" s="3">
         <v>1335</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="3">
+        <f>+Model!K5-Quartr!G5</f>
+        <v>1265</v>
+      </c>
       <c r="I5" s="3">
         <v>1740</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>1670</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1147,12 +1177,17 @@
       <c r="G6" s="3">
         <v>527</v>
       </c>
-      <c r="H6" s="3"/>
+      <c r="H6" s="3">
+        <f>+Model!K6-Quartr!G6</f>
+        <v>500</v>
+      </c>
       <c r="I6" s="3">
         <v>632</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>632</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -1196,12 +1231,17 @@
       <c r="G7" s="3">
         <v>524</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="3">
+        <f>+Model!K7-Quartr!G7</f>
+        <v>441</v>
+      </c>
       <c r="I7" s="3">
         <v>607</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3">
+        <v>530</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1250,7 +1290,9 @@
         <v>4601</v>
       </c>
       <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3">
+        <v>4732</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1299,7 +1341,9 @@
         <v>413</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>873</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1348,7 +1392,9 @@
         <v>1385</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>724</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1397,7 +1443,9 @@
         <v>4785</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>4504</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1446,7 +1494,9 @@
         <v>872</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3">
+        <v>373</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -1495,7 +1545,9 @@
         <v>742</v>
       </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3">
+        <v>1452</v>
+      </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
@@ -1531,20 +1583,34 @@
       <c r="C14" s="10">
         <v>5268</v>
       </c>
-      <c r="D14" s="10"/>
+      <c r="D14" s="10">
+        <f>+Model!I17-Quartr!C14</f>
+        <v>4809</v>
+      </c>
       <c r="E14" s="10">
         <v>6150</v>
       </c>
-      <c r="F14" s="10"/>
+      <c r="F14" s="10">
+        <f>+Model!J17-Quartr!E14</f>
+        <v>5172</v>
+      </c>
       <c r="G14" s="10">
         <v>5412</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="10">
+        <f>+Model!K17-Quartr!G14</f>
+        <v>5207</v>
+      </c>
       <c r="I14" s="10">
         <v>6399</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="J14" s="10">
+        <f>+Model!L17-Quartr!I14</f>
+        <v>5402</v>
+      </c>
+      <c r="K14" s="10">
+        <v>6329</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1624,7 +1690,7 @@
         <v>0.10589239965841157</v>
       </c>
       <c r="H16" s="11" t="e">
-        <f t="shared" ref="H16:J27" si="0">+H3/D3-1</f>
+        <f t="shared" ref="H16:K27" si="0">+H3/D3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I16" s="11">
@@ -1635,7 +1701,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K16" s="3"/>
+      <c r="K16" s="11">
+        <f t="shared" si="0"/>
+        <v>0.1034749034749034</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1688,7 +1757,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K17" s="3"/>
+      <c r="K17" s="11">
+        <f t="shared" si="0"/>
+        <v>0.194685153090699</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1741,7 +1813,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K18" s="3"/>
+      <c r="K18" s="11">
+        <f t="shared" si="0"/>
+        <v>0.25093632958801493</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1794,7 +1869,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K19" s="3"/>
+      <c r="K19" s="11">
+        <f t="shared" si="0"/>
+        <v>0.19924098671726753</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -1847,7 +1925,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="3"/>
+      <c r="K20" s="11">
+        <f t="shared" si="0"/>
+        <v>1.1450381679389388E-2</v>
+      </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -1900,7 +1981,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K21" s="3"/>
+      <c r="K21" s="11">
+        <f t="shared" si="0"/>
+        <v>0.20899335717935608</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
@@ -1953,7 +2037,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K22" s="3"/>
+      <c r="K22" s="11">
+        <f t="shared" si="0"/>
+        <v>5.9466019417475646E-2</v>
+      </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -2006,7 +2093,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K23" s="3"/>
+      <c r="K23" s="11">
+        <f t="shared" si="0"/>
+        <v>7.4183976261127604E-2</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
@@ -2059,7 +2149,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K24" s="3"/>
+      <c r="K24" s="11">
+        <f t="shared" si="0"/>
+        <v>0.20621317621853241</v>
+      </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
@@ -2112,7 +2205,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K25" s="3"/>
+      <c r="K25" s="11">
+        <f t="shared" si="0"/>
+        <v>0.15479876160990713</v>
+      </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
@@ -2165,7 +2261,10 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="3"/>
+      <c r="K26" s="11">
+        <f t="shared" si="0"/>
+        <v>7.158671586715859E-2</v>
+      </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
@@ -2206,19 +2305,22 @@
         <f t="shared" si="1"/>
         <v>2.7334851936218652E-2</v>
       </c>
-      <c r="H27" s="12" t="e">
+      <c r="H27" s="12">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>8.2761488875026101E-2</v>
       </c>
       <c r="I27" s="12">
         <f t="shared" si="0"/>
         <v>4.0487804878048816E-2</v>
       </c>
-      <c r="J27" s="12" t="e">
+      <c r="J27" s="12">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="3"/>
+        <v>4.4470224284609339E-2</v>
+      </c>
+      <c r="K27" s="12">
+        <f t="shared" si="0"/>
+        <v>0.16943828529194382</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
@@ -7478,7 +7580,10 @@
       <c r="K3" s="3">
         <v>2586</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <f>+T3-K3</f>
+        <v>2678</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -7536,7 +7641,10 @@
       <c r="K4" s="3">
         <v>3441</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <f t="shared" ref="L4:L31" si="2">+T4-K4</f>
+        <v>3763</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -7594,7 +7702,10 @@
       <c r="K5" s="3">
         <v>2600</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <f t="shared" si="2"/>
+        <v>3080</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -7652,7 +7763,10 @@
       <c r="K6" s="3">
         <v>1027</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <f t="shared" si="2"/>
+        <v>1202</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -7710,7 +7824,10 @@
       <c r="K7" s="3">
         <v>965</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <f t="shared" si="2"/>
+        <v>1078</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -7768,7 +7885,10 @@
       <c r="K8" s="3">
         <v>5702</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="3">
+        <f t="shared" si="2"/>
+        <v>6504</v>
+      </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -7826,7 +7946,10 @@
       <c r="K9" s="3">
         <v>3456</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>3701</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -7884,7 +8007,10 @@
       <c r="K10" s="3">
         <v>490</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <f t="shared" si="2"/>
+        <v>512</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -7942,7 +8068,10 @@
       <c r="K11" s="3">
         <v>456</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <f t="shared" si="2"/>
+        <v>470</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -8000,7 +8129,10 @@
       <c r="K12" s="3">
         <v>185</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <f t="shared" si="2"/>
+        <v>230</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -8058,7 +8190,10 @@
       <c r="K13" s="3">
         <v>330</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <f t="shared" si="2"/>
+        <v>384</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -8159,7 +8294,10 @@
       <c r="K14" s="3">
         <v>7414</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <f t="shared" si="2"/>
+        <v>8433</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -8260,7 +8398,10 @@
       <c r="K15" s="3">
         <v>621</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <f t="shared" si="2"/>
+        <v>761</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -8361,7 +8502,10 @@
       <c r="K16" s="3">
         <v>2584</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <f t="shared" si="2"/>
+        <v>2607</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -8462,7 +8606,10 @@
       <c r="K17" s="10">
         <v>10619</v>
       </c>
-      <c r="L17" s="10"/>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>11801</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -8563,7 +8710,10 @@
       <c r="K18" s="3">
         <v>3680</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <f t="shared" si="2"/>
+        <v>4302</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -8644,27 +8794,27 @@
         <v>23</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" ref="C19:H19" si="2">+C17-C18</f>
+        <f t="shared" ref="C19:H19" si="3">+C17-C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6973</v>
       </c>
       <c r="H19" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7063</v>
       </c>
       <c r="I19" s="3">
@@ -8672,30 +8822,33 @@
         <v>6771</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" ref="J19:K19" si="3">+J17-J18</f>
+        <f t="shared" ref="J19:L19" si="4">+J17-J18</f>
         <v>7548</v>
       </c>
       <c r="K19" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6939</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="3">
+        <f t="shared" si="4"/>
+        <v>7499</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
-        <f t="shared" ref="O19:R19" si="4">+O17-O18</f>
+        <f t="shared" ref="O19:R19" si="5">+O17-O18</f>
         <v>0</v>
       </c>
       <c r="P19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11176</v>
       </c>
       <c r="Q19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13716</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14036</v>
       </c>
       <c r="S19" s="3">
@@ -8788,7 +8941,10 @@
       <c r="K20" s="3">
         <v>2725</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3">
+        <f t="shared" si="2"/>
+        <v>3006</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -8889,7 +9045,10 @@
       <c r="K21" s="3">
         <v>875</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="3">
+        <f t="shared" si="2"/>
+        <v>1121</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -8990,7 +9149,10 @@
       <c r="K22" s="3">
         <v>970</v>
       </c>
-      <c r="L22" s="3"/>
+      <c r="L22" s="3">
+        <f t="shared" si="2"/>
+        <v>1042</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -9091,7 +9253,10 @@
       <c r="K23" s="3">
         <v>11</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="3">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -9174,27 +9339,27 @@
         <v>28</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" ref="C24:H24" si="5">+C19-SUM(C20:C23)</f>
+        <f t="shared" ref="C24:H24" si="6">+C19-SUM(C20:C23)</f>
         <v>0</v>
       </c>
       <c r="D24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2655</v>
       </c>
       <c r="H24" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2139</v>
       </c>
       <c r="I24" s="3">
@@ -9202,41 +9367,44 @@
         <v>2206</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24:T24" si="6">+J19-SUM(J20:J23)</f>
+        <f t="shared" ref="J24:T24" si="7">+J19-SUM(J20:J23)</f>
         <v>2261</v>
       </c>
       <c r="K24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2358</v>
       </c>
-      <c r="L24" s="3"/>
+      <c r="L24" s="3">
+        <f t="shared" si="7"/>
+        <v>2134</v>
+      </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="O24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3753</v>
       </c>
       <c r="Q24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5031</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4794</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4467</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4492</v>
       </c>
       <c r="U24" s="3"/>
@@ -9321,7 +9489,10 @@
       <c r="K25" s="3">
         <v>739</v>
       </c>
-      <c r="L25" s="3"/>
+      <c r="L25" s="3">
+        <f t="shared" si="2"/>
+        <v>118</v>
+      </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -9422,7 +9593,10 @@
       <c r="K26" s="3">
         <v>581</v>
       </c>
-      <c r="L26" s="3"/>
+      <c r="L26" s="3">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -9523,7 +9697,10 @@
       <c r="K27" s="3">
         <v>24</v>
       </c>
-      <c r="L27" s="3"/>
+      <c r="L27" s="3">
+        <f t="shared" si="2"/>
+        <v>-22</v>
+      </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -9604,27 +9781,27 @@
         <v>32</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" ref="C28:H28" si="7">+C24-C25+C26+C27</f>
+        <f t="shared" ref="C28:H28" si="8">+C24-C25+C26+C27</f>
         <v>0</v>
       </c>
       <c r="D28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2629</v>
       </c>
       <c r="H28" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2026</v>
       </c>
       <c r="I28" s="3">
@@ -9632,41 +9809,44 @@
         <v>2091</v>
       </c>
       <c r="J28" s="3">
-        <f t="shared" ref="J28:T28" si="8">+J24-J25+J26+J27</f>
+        <f t="shared" ref="J28:T28" si="9">+J24-J25+J26+J27</f>
         <v>2398</v>
       </c>
       <c r="K28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2224</v>
       </c>
-      <c r="L28" s="3"/>
+      <c r="L28" s="3">
+        <f t="shared" si="9"/>
+        <v>2126</v>
+      </c>
       <c r="M28" s="3"/>
       <c r="N28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2943</v>
       </c>
       <c r="Q28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4758</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4655</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4489</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4350</v>
       </c>
       <c r="U28" s="3"/>
@@ -9751,7 +9931,10 @@
       <c r="K29" s="3">
         <v>428</v>
       </c>
-      <c r="L29" s="3"/>
+      <c r="L29" s="3">
+        <f t="shared" si="2"/>
+        <v>458</v>
+      </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -9832,19 +10015,19 @@
         <v>34</v>
       </c>
       <c r="C30" s="3">
-        <f t="shared" ref="C30:F30" si="9">+C28-C29</f>
+        <f t="shared" ref="C30:F30" si="10">+C28-C29</f>
         <v>0</v>
       </c>
       <c r="D30" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E30" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F30" s="3">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G30" s="3">
@@ -9852,35 +10035,38 @@
         <v>2160</v>
       </c>
       <c r="H30" s="3">
-        <f t="shared" ref="H30:K30" si="10">+H28-H29</f>
+        <f t="shared" ref="H30:L30" si="11">+H28-H29</f>
         <v>1658</v>
       </c>
       <c r="I30" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1729</v>
       </c>
       <c r="J30" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>2033</v>
       </c>
       <c r="K30" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1796</v>
       </c>
-      <c r="L30" s="3"/>
+      <c r="L30" s="3">
+        <f t="shared" si="11"/>
+        <v>1668</v>
+      </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3">
-        <f t="shared" ref="P30:R30" si="11">+P28-P29</f>
+        <f t="shared" ref="P30:R30" si="12">+P28-P29</f>
         <v>2449</v>
       </c>
       <c r="Q30" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3911</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>3818</v>
       </c>
       <c r="S30" s="3">
@@ -9973,7 +10159,10 @@
       <c r="K31" s="3">
         <v>17</v>
       </c>
-      <c r="L31" s="3"/>
+      <c r="L31" s="3">
+        <f t="shared" si="2"/>
+        <v>-37</v>
+      </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -10054,27 +10243,27 @@
         <v>36</v>
       </c>
       <c r="C32" s="3">
-        <f t="shared" ref="C32:H32" si="12">+C30-C31</f>
+        <f t="shared" ref="C32:H32" si="13">+C30-C31</f>
         <v>0</v>
       </c>
       <c r="D32" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1505</v>
       </c>
       <c r="H32" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>850</v>
       </c>
       <c r="I32" s="3">
@@ -10082,30 +10271,33 @@
         <v>457</v>
       </c>
       <c r="J32" s="3">
-        <f t="shared" ref="J32:K32" si="13">+J30-J31</f>
+        <f t="shared" ref="J32:L32" si="14">+J30-J31</f>
         <v>2293</v>
       </c>
       <c r="K32" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1779</v>
       </c>
-      <c r="L32" s="3"/>
+      <c r="L32" s="3">
+        <f t="shared" si="14"/>
+        <v>1705</v>
+      </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3">
-        <f t="shared" ref="O32:R32" si="14">+O30-O31</f>
+        <f t="shared" ref="O32:R32" si="15">+O30-O31</f>
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2079</v>
       </c>
       <c r="Q32" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>301</v>
       </c>
       <c r="R32" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2355</v>
       </c>
       <c r="S32" s="3">
@@ -10254,27 +10446,27 @@
         <v>37</v>
       </c>
       <c r="C34" s="13" t="e">
-        <f t="shared" ref="C34:H34" si="15">+C32/C35</f>
+        <f t="shared" ref="C34:H34" si="16">+C32/C35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D34" s="13" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E34" s="13" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F34" s="13" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G34" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.6361884743387636</v>
       </c>
       <c r="H34" s="13">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.4746703678001389</v>
       </c>
       <c r="I34" s="13">
@@ -10282,33 +10474,36 @@
         <v>0.77999658644819936</v>
       </c>
       <c r="J34" s="13">
-        <f t="shared" ref="J34:K34" si="16">+J32/J35</f>
+        <f t="shared" ref="J34:K34" si="17">+J32/J35</f>
         <v>3.9083006647349579</v>
       </c>
       <c r="K34" s="13">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>3.027569775357386</v>
       </c>
-      <c r="L34" s="13"/>
+      <c r="L34" s="13">
+        <f t="shared" ref="L34" si="18">+L32/L35</f>
+        <v>2.9016337644656227</v>
+      </c>
       <c r="M34" s="3"/>
       <c r="N34" s="13" t="e">
-        <f t="shared" ref="N34:R34" si="17">+N32/N35</f>
+        <f t="shared" ref="N34:R34" si="19">+N32/N35</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O34" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P34" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q34" s="13" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="13">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.0857043719639137</v>
       </c>
       <c r="S34" s="13">
@@ -10401,7 +10596,9 @@
       <c r="K35" s="5">
         <v>587.6</v>
       </c>
-      <c r="L35" s="5"/>
+      <c r="L35" s="5">
+        <v>587.6</v>
+      </c>
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -10557,37 +10754,40 @@
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="11" t="e">
-        <f t="shared" ref="F37:K42" si="18">+F8/D8-1</f>
+        <f t="shared" ref="F37:K42" si="20">+F8/D8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H37" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I37" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.5186466743560167E-2</v>
       </c>
       <c r="J37" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.12595419847328237</v>
       </c>
       <c r="K37" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>7.9719750047339444E-2</v>
       </c>
-      <c r="L37" s="11"/>
+      <c r="L37" s="11">
+        <f t="shared" ref="L37:L42" si="21">+L8/J8-1</f>
+        <v>4.987893462469728E-2</v>
+      </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="11">
-        <f t="shared" ref="R37" si="19">+R8/Q8-1</f>
+        <f t="shared" ref="R37" si="22">+R8/Q8-1</f>
         <v>6.65603826225587E-2</v>
       </c>
       <c r="S37" s="11">
@@ -10663,45 +10863,48 @@
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G38" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H38" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-7.5319622012228971E-2</v>
       </c>
       <c r="J38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2.4977960622979634E-2</v>
       </c>
       <c r="K38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>3.8773669972948621E-2</v>
       </c>
-      <c r="L38" s="11"/>
+      <c r="L38" s="11">
+        <f t="shared" si="21"/>
+        <v>6.1066513761467878E-2</v>
+      </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="11">
-        <f t="shared" ref="R38:T42" si="20">+R9/Q9-1</f>
+        <f t="shared" ref="R38:T42" si="23">+R9/Q9-1</f>
         <v>2.5776886724904191E-3</v>
       </c>
       <c r="S38" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-2.6567633195257789E-2</v>
       </c>
       <c r="T38" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>5.018341892883349E-2</v>
       </c>
       <c r="U38" s="3"/>
@@ -10769,45 +10972,48 @@
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G39" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H39" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I39" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2.9354207436399271E-2</v>
       </c>
       <c r="J39" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.3385214007781991E-2</v>
       </c>
       <c r="K39" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-6.84410646387833E-2</v>
       </c>
-      <c r="L39" s="11"/>
+      <c r="L39" s="11">
+        <f t="shared" si="21"/>
+        <v>-8.8967971530249157E-2</v>
+      </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.21733966745843225</v>
       </c>
       <c r="S39" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>6.1463414634146396E-2</v>
       </c>
       <c r="T39" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-7.9044117647058876E-2</v>
       </c>
       <c r="U39" s="3"/>
@@ -10875,45 +11081,48 @@
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G40" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H40" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I40" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.10026385224274414</v>
       </c>
       <c r="J40" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.1048780487804879</v>
       </c>
       <c r="K40" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>9.3525179856115193E-2</v>
       </c>
-      <c r="L40" s="11"/>
+      <c r="L40" s="11">
+        <f t="shared" si="21"/>
+        <v>3.7527593818984517E-2</v>
+      </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-0.18068535825545173</v>
       </c>
       <c r="S40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>0.10266159695817501</v>
       </c>
       <c r="T40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>6.4367816091954078E-2</v>
       </c>
       <c r="U40" s="3"/>
@@ -10981,45 +11190,48 @@
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G41" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H41" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I41" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-4.2452830188679291E-2</v>
       </c>
       <c r="J41" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4.484304932735439E-3</v>
       </c>
       <c r="K41" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-8.8669950738916259E-2</v>
       </c>
-      <c r="L41" s="11"/>
+      <c r="L41" s="11">
+        <f t="shared" si="21"/>
+        <v>2.6785714285714191E-2</v>
+      </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-4.6052631578947345E-2</v>
       </c>
       <c r="S41" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-1.8390804597701149E-2</v>
       </c>
       <c r="T41" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-2.8103044496487151E-2</v>
       </c>
       <c r="U41" s="3"/>
@@ -11087,45 +11299,48 @@
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G42" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H42" s="11" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I42" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1.2539184952978122E-2</v>
       </c>
       <c r="J42" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.16618075801749277</v>
       </c>
       <c r="K42" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2.1671826625387025E-2</v>
       </c>
-      <c r="L42" s="11"/>
+      <c r="L42" s="11">
+        <f t="shared" si="21"/>
+        <v>-4.0000000000000036E-2</v>
+      </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-1.6344725111441361E-2</v>
       </c>
       <c r="S42" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>9.2145015105740136E-2</v>
       </c>
       <c r="T42" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>-1.2448132780082943E-2</v>
       </c>
       <c r="U42" s="3"/>
@@ -11193,40 +11408,43 @@
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
       <c r="F43" s="12" t="e">
-        <f t="shared" ref="F43" si="21">+F17/D17-1</f>
+        <f t="shared" ref="F43" si="24">+F17/D17-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G43" s="12" t="e">
-        <f t="shared" ref="G43:H43" si="22">+G17/E17-1</f>
+        <f t="shared" ref="G43:H43" si="25">+G17/E17-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H43" s="12" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I43" s="12">
-        <f t="shared" ref="I43:K43" si="23">+I17/G17-1</f>
+        <f t="shared" ref="I43:K43" si="26">+I17/G17-1</f>
         <v>-1.4088641033166982E-2</v>
       </c>
       <c r="J43" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>8.9177489177489244E-2</v>
       </c>
       <c r="K43" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>5.3785848962984995E-2</v>
       </c>
-      <c r="L43" s="12"/>
+      <c r="L43" s="12">
+        <f t="shared" ref="L43" si="27">+L17/J17-1</f>
+        <v>4.2307012895248297E-2</v>
+      </c>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="12">
-        <f t="shared" ref="Q43:R43" si="24">+Q17/P17-1</f>
+        <f t="shared" ref="Q43:R43" si="28">+Q17/P17-1</f>
         <v>0.19136613326964413</v>
       </c>
       <c r="R43" s="12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>3.3228086002105028E-2</v>
       </c>
       <c r="S43" s="12">
@@ -11299,27 +11517,27 @@
         <v>51</v>
       </c>
       <c r="C44" s="11" t="e">
-        <f t="shared" ref="C44:H44" si="25">+C19/C17</f>
+        <f t="shared" ref="C44:H44" si="29">+C19/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D44" s="11" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E44" s="11" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F44" s="11" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G44" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.68222287447412189</v>
       </c>
       <c r="H44" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.67946127946127943</v>
       </c>
       <c r="I44" s="11">
@@ -11327,41 +11545,44 @@
         <v>0.67192616850253051</v>
       </c>
       <c r="J44" s="11">
-        <f t="shared" ref="J44:S44" si="26">+J19/J17</f>
+        <f t="shared" ref="J44:S44" si="30">+J19/J17</f>
         <v>0.66666666666666663</v>
       </c>
       <c r="K44" s="11">
-        <f t="shared" ref="K44" si="27">+K19/K17</f>
+        <f t="shared" ref="K44:L44" si="31">+K19/K17</f>
         <v>0.65345136076843391</v>
       </c>
-      <c r="L44" s="11"/>
+      <c r="L44" s="11">
+        <f t="shared" si="31"/>
+        <v>0.63545462248961948</v>
+      </c>
       <c r="M44" s="3"/>
       <c r="N44" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O44" s="11" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P44" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.6673035586338667</v>
       </c>
       <c r="Q44" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.6874154262516915</v>
       </c>
       <c r="R44" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.68083042297244856</v>
       </c>
       <c r="S44" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>0.66914341791672505</v>
       </c>
       <c r="T44" s="11">
-        <f t="shared" ref="T44" si="28">+T19/T17</f>
+        <f t="shared" ref="T44" si="32">+T19/T17</f>
         <v>0.64397859054415696</v>
       </c>
       <c r="U44" s="3"/>
@@ -11426,27 +11647,27 @@
         <v>52</v>
       </c>
       <c r="C45" s="11" t="e">
-        <f t="shared" ref="C45:H45" si="29">+C24/C17</f>
+        <f t="shared" ref="C45:H45" si="33">+C24/C17</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D45" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E45" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F45" s="11" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.25975931904901672</v>
       </c>
       <c r="H45" s="11">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.20577200577200577</v>
       </c>
       <c r="I45" s="11">
@@ -11454,41 +11675,44 @@
         <v>0.21891435943237075</v>
       </c>
       <c r="J45" s="11">
-        <f t="shared" ref="J45:S45" si="30">+J24/J17</f>
+        <f t="shared" ref="J45:S45" si="34">+J24/J17</f>
         <v>0.1996996996996997</v>
       </c>
       <c r="K45" s="11">
-        <f t="shared" ref="K45" si="31">+K24/K17</f>
+        <f t="shared" ref="K45:L45" si="35">+K24/K17</f>
         <v>0.22205480742066108</v>
       </c>
-      <c r="L45" s="11"/>
+      <c r="L45" s="11">
+        <f t="shared" si="35"/>
+        <v>0.18083213287009575</v>
+      </c>
       <c r="M45" s="3"/>
       <c r="N45" s="11" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O45" s="11" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P45" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.22408645808454741</v>
       </c>
       <c r="Q45" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.25214253495714928</v>
       </c>
       <c r="R45" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.23253783469150174</v>
       </c>
       <c r="S45" s="11">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>0.20874807233982898</v>
       </c>
       <c r="T45" s="11">
-        <f t="shared" ref="T45" si="32">+T24/T17</f>
+        <f t="shared" ref="T45" si="36">+T24/T17</f>
         <v>0.20035682426404997</v>
       </c>
       <c r="U45" s="3"/>
@@ -11553,27 +11777,27 @@
         <v>53</v>
       </c>
       <c r="C46" s="11" t="e">
-        <f t="shared" ref="C46:H46" si="33">+C29/C28</f>
+        <f t="shared" ref="C46:H46" si="37">+C29/C28</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D46" s="11" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E46" s="11" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F46" s="11" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G46" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.1783948269303918</v>
       </c>
       <c r="H46" s="11">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.18163869693978282</v>
       </c>
       <c r="I46" s="11">
@@ -11581,41 +11805,44 @@
         <v>0.17312290769966523</v>
       </c>
       <c r="J46" s="11">
-        <f t="shared" ref="J46:S46" si="34">+J29/J28</f>
+        <f t="shared" ref="J46:S46" si="38">+J29/J28</f>
         <v>0.15221017514595497</v>
       </c>
       <c r="K46" s="11">
-        <f t="shared" ref="K46" si="35">+K29/K28</f>
+        <f t="shared" ref="K46:L46" si="39">+K29/K28</f>
         <v>0.19244604316546762</v>
       </c>
-      <c r="L46" s="11"/>
+      <c r="L46" s="11">
+        <f t="shared" si="39"/>
+        <v>0.21542803386641579</v>
+      </c>
       <c r="M46" s="3"/>
       <c r="N46" s="11" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O46" s="11" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P46" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.16785592932381924</v>
       </c>
       <c r="Q46" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.17801597309794032</v>
       </c>
       <c r="R46" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.17980665950590763</v>
       </c>
       <c r="S46" s="11">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>0.16195143684562263</v>
       </c>
       <c r="T46" s="11">
-        <f t="shared" ref="T46" si="36">+T29/T28</f>
+        <f t="shared" ref="T46" si="40">+T29/T28</f>
         <v>0.20367816091954022</v>
       </c>
       <c r="U46" s="3"/>
